--- a/8-1_Teacher_subject.xlsx
+++ b/8-1_Teacher_subject.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17691"/>
+    <workbookView windowWidth="21600" windowHeight="10491"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="613">
+  <si>
+    <t>学校代码</t>
+  </si>
+  <si>
+    <t>学校名称</t>
+  </si>
   <si>
     <t>年级</t>
   </si>
@@ -35,12 +41,6 @@
     <t>班别</t>
   </si>
   <si>
-    <t>学校代码</t>
-  </si>
-  <si>
-    <t>学校名称</t>
-  </si>
-  <si>
     <t>语文科任</t>
   </si>
   <si>
@@ -65,12 +65,12 @@
     <t>生物科任</t>
   </si>
   <si>
+    <t>开平市第二中学</t>
+  </si>
+  <si>
     <t>01</t>
   </si>
   <si>
-    <t>开平市第二中学</t>
-  </si>
-  <si>
     <t>何明爱</t>
   </si>
   <si>
@@ -188,16 +188,16 @@
     <t>谢雪宁</t>
   </si>
   <si>
+    <t>甄植强</t>
+  </si>
+  <si>
     <t>钟燕青</t>
   </si>
   <si>
-    <t>甄植强</t>
-  </si>
-  <si>
     <t>吴锐锋</t>
   </si>
   <si>
-    <t>陈祖益</t>
+    <t>张妙颖</t>
   </si>
   <si>
     <t>颜梓兴</t>
@@ -395,18 +395,21 @@
     <t>谢彩萍</t>
   </si>
   <si>
+    <t>谢珠仙</t>
+  </si>
+  <si>
     <t>谭丽容</t>
   </si>
   <si>
-    <t>谢珠仙</t>
+    <t>吴艳梨</t>
+  </si>
+  <si>
+    <t>蒋琴</t>
   </si>
   <si>
     <t>张晋毅</t>
   </si>
   <si>
-    <t>蒋琴</t>
-  </si>
-  <si>
     <t>李健洪</t>
   </si>
   <si>
@@ -419,7 +422,7 @@
     <t>谭简尧</t>
   </si>
   <si>
-    <t>唐小玲</t>
+    <t>谭艳玲</t>
   </si>
   <si>
     <t>卢剑平</t>
@@ -509,7 +512,7 @@
     <t>麦朝杰</t>
   </si>
   <si>
-    <t>缺岗</t>
+    <t>梁挺进</t>
   </si>
   <si>
     <t>何惠娟</t>
@@ -566,7 +569,7 @@
     <t>冯春燕</t>
   </si>
   <si>
-    <t>梁灿雄</t>
+    <t>唐荣贵</t>
   </si>
   <si>
     <t>关秀君</t>
@@ -587,9 +590,6 @@
     <t>劳珠玲</t>
   </si>
   <si>
-    <t>唐荣贵</t>
-  </si>
-  <si>
     <t>吴银环</t>
   </si>
   <si>
@@ -734,7 +734,7 @@
     <t>江陈枫</t>
   </si>
   <si>
-    <t>刘春秀</t>
+    <t>李忠坚</t>
   </si>
   <si>
     <t>李晓童</t>
@@ -752,9 +752,6 @@
     <t>黄靖茵</t>
   </si>
   <si>
-    <t>李忠坚</t>
-  </si>
-  <si>
     <t>周小愉</t>
   </si>
   <si>
@@ -770,7 +767,7 @@
     <t>李瑞芬</t>
   </si>
   <si>
-    <t>罗映</t>
+    <t>陈淑欣</t>
   </si>
   <si>
     <t>方晓红</t>
@@ -935,10 +932,7 @@
     <t>莫佩华</t>
   </si>
   <si>
-    <t>严佩玲</t>
-  </si>
-  <si>
-    <t>开平市东河中学</t>
+    <t>开平市东河初级中学</t>
   </si>
   <si>
     <t>梁秀英</t>
@@ -950,6 +944,9 @@
     <t>方群用</t>
   </si>
   <si>
+    <t>曹德棠</t>
+  </si>
+  <si>
     <t>黎洁琼</t>
   </si>
   <si>
@@ -974,12 +971,12 @@
     <t>谢彩裳</t>
   </si>
   <si>
-    <t>伍宝珠</t>
-  </si>
-  <si>
     <t>刘丽婵</t>
   </si>
   <si>
+    <t>邓新敏</t>
+  </si>
+  <si>
     <t>麦秀丽</t>
   </si>
   <si>
@@ -989,30 +986,30 @@
     <t>张玉霞</t>
   </si>
   <si>
+    <t>梁活明</t>
+  </si>
+  <si>
+    <t>余婵娟</t>
+  </si>
+  <si>
+    <t>梁雅冰</t>
+  </si>
+  <si>
+    <t>熊艳嫦</t>
+  </si>
+  <si>
+    <t>蓝明秋</t>
+  </si>
+  <si>
+    <t>凌海斌</t>
+  </si>
+  <si>
     <t>温丽玲</t>
   </si>
   <si>
-    <t>邓新敏</t>
-  </si>
-  <si>
-    <t>余婵娟</t>
-  </si>
-  <si>
-    <t>梁雅冰</t>
-  </si>
-  <si>
-    <t>熊艳嫦</t>
-  </si>
-  <si>
-    <t>凌海斌</t>
-  </si>
-  <si>
     <t>谭雪贤</t>
   </si>
   <si>
-    <t>谭艳玲</t>
-  </si>
-  <si>
     <t>张裕坚</t>
   </si>
   <si>
@@ -1022,7 +1019,7 @@
     <t>周新红</t>
   </si>
   <si>
-    <t>开平市新荻中学</t>
+    <t>开平市新荻初级中学</t>
   </si>
   <si>
     <t>司徒苑莲</t>
@@ -1076,7 +1073,7 @@
     <t>蹇敦洪</t>
   </si>
   <si>
-    <t>谭艳芬</t>
+    <t>李景欢</t>
   </si>
   <si>
     <t>练悦华</t>
@@ -1097,7 +1094,7 @@
     <t>谭东英</t>
   </si>
   <si>
-    <t>开平市港口中学</t>
+    <t>开平市港口初级中学</t>
   </si>
   <si>
     <t>雷一飞</t>
@@ -1208,7 +1205,7 @@
     <t>颜俏俐</t>
   </si>
   <si>
-    <t>翠山湖实验学校</t>
+    <t>开平市翠山湖实验学校</t>
   </si>
   <si>
     <t>梁优婷</t>
@@ -1229,25 +1226,28 @@
     <t>赵茂英</t>
   </si>
   <si>
+    <t>李惠琼</t>
+  </si>
+  <si>
+    <t>黄海安</t>
+  </si>
+  <si>
+    <t>张雪兰</t>
+  </si>
+  <si>
+    <t>李碧婵</t>
+  </si>
+  <si>
+    <t>李素芳</t>
+  </si>
+  <si>
     <t>许结仪</t>
   </si>
   <si>
-    <t>黄海安</t>
-  </si>
-  <si>
-    <t>张雪兰</t>
-  </si>
-  <si>
-    <t>李碧婵</t>
-  </si>
-  <si>
-    <t>李素芳</t>
-  </si>
-  <si>
     <t>陈寅效</t>
   </si>
   <si>
-    <t>开平市月山中学</t>
+    <t>开平市月山初级中学</t>
   </si>
   <si>
     <t>黎球安</t>
@@ -1304,7 +1304,7 @@
     <t>梁珊姗</t>
   </si>
   <si>
-    <t>开平市月山大岗校区</t>
+    <t>开平市月山初级中学大</t>
   </si>
   <si>
     <t>张惠玲</t>
@@ -1328,7 +1328,7 @@
     <t>罗润森</t>
   </si>
   <si>
-    <t>开平市庆扬中学</t>
+    <t>开平市庆扬初级中学</t>
   </si>
   <si>
     <t>邓金叶</t>
@@ -1409,7 +1409,7 @@
     <t>王锦虹</t>
   </si>
   <si>
-    <t>开平市沙冈中学</t>
+    <t>开平市沙冈初级中学</t>
   </si>
   <si>
     <t>赖春芳</t>
@@ -1493,7 +1493,7 @@
     <t>黄宏韧</t>
   </si>
   <si>
-    <t>开平市长沙实验学校</t>
+    <t>开平市长沙街道办事处</t>
   </si>
   <si>
     <t>梁健玲</t>
@@ -1505,7 +1505,7 @@
     <t>黄惠卿</t>
   </si>
   <si>
-    <t>邓红艳</t>
+    <t>梁子清</t>
   </si>
   <si>
     <t>刘国卫</t>
@@ -1520,9 +1520,6 @@
     <t>陈红蕊</t>
   </si>
   <si>
-    <t>杨康友</t>
-  </si>
-  <si>
     <t>徐桂清</t>
   </si>
   <si>
@@ -1577,7 +1574,7 @@
     <t>梁彦亮</t>
   </si>
   <si>
-    <t>开平市龙胜中学</t>
+    <t>开平市龙胜初级中学</t>
   </si>
   <si>
     <t>陈转换</t>
@@ -1592,7 +1589,7 @@
     <t>梁沃超</t>
   </si>
   <si>
-    <t>劳瑞恩</t>
+    <t>李嘉杰</t>
   </si>
   <si>
     <t>伍琬滢</t>
@@ -1610,7 +1607,7 @@
     <t>张艳芳</t>
   </si>
   <si>
-    <t>张伟贞</t>
+    <t>叶梅</t>
   </si>
   <si>
     <t>张静仪</t>
@@ -1628,7 +1625,7 @@
     <t>徐玉琼</t>
   </si>
   <si>
-    <t>开平市大沙中学</t>
+    <t>开平市大沙初级中学</t>
   </si>
   <si>
     <t>梁爱芹</t>
@@ -1640,7 +1637,7 @@
     <t>李坚钊</t>
   </si>
   <si>
-    <t>熊建彬</t>
+    <t>梁文佳</t>
   </si>
   <si>
     <t>胡钰滢</t>
@@ -1658,16 +1655,13 @@
     <t>梁志娜</t>
   </si>
   <si>
-    <t>梁文佳</t>
-  </si>
-  <si>
     <t>张飞灿</t>
   </si>
   <si>
     <t>陈景婵</t>
   </si>
   <si>
-    <t>开平市宝树中学</t>
+    <t>开平市宝树初级中学</t>
   </si>
   <si>
     <t>黄理燕</t>
@@ -1685,7 +1679,7 @@
     <t>李秋敏</t>
   </si>
   <si>
-    <t>黄柳银</t>
+    <t>张景济</t>
   </si>
   <si>
     <t>龚秀珍</t>
@@ -1697,7 +1691,7 @@
     <t>杨伯成</t>
   </si>
   <si>
-    <t>开平市百合中学</t>
+    <t>开平市百合初级中学</t>
   </si>
   <si>
     <t>黄斯慧</t>
@@ -1721,15 +1715,21 @@
     <t>方宏伟</t>
   </si>
   <si>
+    <t>关妙莲</t>
+  </si>
+  <si>
+    <t>张荣健</t>
+  </si>
+  <si>
     <t>谭锦珠</t>
   </si>
   <si>
-    <t>关妙莲</t>
-  </si>
-  <si>
     <t>刘晓玲</t>
   </si>
   <si>
+    <t>司徒秀匀</t>
+  </si>
+  <si>
     <t>开平市蚬冈学校</t>
   </si>
   <si>
@@ -1757,33 +1757,36 @@
     <t>关惠玲</t>
   </si>
   <si>
-    <t>开平市金鸡中学</t>
+    <t>开平市金鸡初级中学</t>
+  </si>
+  <si>
+    <t>罗珮瑜</t>
+  </si>
+  <si>
+    <t>周精英</t>
+  </si>
+  <si>
+    <t>刘永洪</t>
+  </si>
+  <si>
+    <t>刘杰深</t>
+  </si>
+  <si>
+    <t>刘君域</t>
+  </si>
+  <si>
+    <t>陈昌武</t>
+  </si>
+  <si>
+    <t>甄锦莲</t>
+  </si>
+  <si>
+    <t>黄润胜</t>
   </si>
   <si>
     <t>关健明</t>
   </si>
   <si>
-    <t>周精英</t>
-  </si>
-  <si>
-    <t>刘永洪</t>
-  </si>
-  <si>
-    <t>刘杰深</t>
-  </si>
-  <si>
-    <t>刘君域</t>
-  </si>
-  <si>
-    <t>陈昌武</t>
-  </si>
-  <si>
-    <t>甄锦莲</t>
-  </si>
-  <si>
-    <t>黄润胜</t>
-  </si>
-  <si>
     <t>梁卓悦</t>
   </si>
   <si>
@@ -1814,7 +1817,7 @@
     <t>谭杰媚</t>
   </si>
   <si>
-    <t>陈艺琳</t>
+    <t>杨怡莉</t>
   </si>
   <si>
     <t>关嘉仪</t>
@@ -1835,7 +1838,7 @@
     <t>谭美琪</t>
   </si>
   <si>
-    <t>莫雪玉</t>
+    <t>关桂英</t>
   </si>
   <si>
     <t>方静屏</t>
@@ -1850,16 +1853,19 @@
     <t>吴翠锦</t>
   </si>
   <si>
+    <t>谢芸</t>
+  </si>
+  <si>
+    <t>朱红梅</t>
+  </si>
+  <si>
+    <t>洪恩旺</t>
+  </si>
+  <si>
     <t>黄强</t>
   </si>
   <si>
-    <t>朱红梅</t>
-  </si>
-  <si>
-    <t>洪恩旺</t>
-  </si>
-  <si>
-    <t>黄翠华</t>
+    <t>黄晶晶</t>
   </si>
 </sst>
 </file>
@@ -2468,14 +2474,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2530,14 +2530,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2731,25 +2724,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3026,10 +3019,10 @@
   <dimension ref="A1:L178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="4.74774774774775" customWidth="1"/>
-    <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="21.0720720720721" customWidth="1"/>
-    <col min="4" max="4" width="28.1261261261261" customWidth="1"/>
+    <col min="1" max="1" width="9.5045045045045" customWidth="1"/>
+    <col min="2" max="2" width="21.7027027027027" customWidth="1"/>
+    <col min="3" max="3" width="5.48648648648649" customWidth="1"/>
+    <col min="4" max="4" width="6.63963963963964" customWidth="1"/>
     <col min="5" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3040,46 +3033,46 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>8</v>
+        <v>78302</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2">
-        <v>78302</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -3111,16 +3104,16 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>8</v>
+        <v>78302</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
-      </c>
-      <c r="C3">
-        <v>78302</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -3149,16 +3142,16 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>8</v>
+        <v>78302</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4">
-        <v>78302</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
@@ -3187,16 +3180,16 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>8</v>
+        <v>78302</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
-      </c>
-      <c r="C5">
-        <v>78302</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
@@ -3225,16 +3218,16 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>8</v>
+        <v>78302</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
         <v>33</v>
-      </c>
-      <c r="C6">
-        <v>78302</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
@@ -3263,16 +3256,16 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>8</v>
+        <v>78302</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
         <v>40</v>
-      </c>
-      <c r="C7">
-        <v>78302</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
@@ -3301,16 +3294,16 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>8</v>
+        <v>78302</v>
       </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
         <v>41</v>
-      </c>
-      <c r="C8">
-        <v>78302</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>42</v>
@@ -3339,16 +3332,16 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>8</v>
+        <v>78302</v>
       </c>
       <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
         <v>46</v>
-      </c>
-      <c r="C9">
-        <v>78302</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
       </c>
       <c r="E9" t="s">
         <v>47</v>
@@ -3377,16 +3370,16 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>8</v>
+        <v>78303</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C10">
-        <v>78303</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
         <v>50</v>
@@ -3415,16 +3408,16 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>8</v>
+        <v>78303</v>
       </c>
       <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
-      </c>
-      <c r="C11">
-        <v>78303</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>58</v>
@@ -3453,16 +3446,16 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>8</v>
+        <v>78303</v>
       </c>
       <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
         <v>23</v>
-      </c>
-      <c r="C12">
-        <v>78303</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
       </c>
       <c r="E12" t="s">
         <v>59</v>
@@ -3474,10 +3467,10 @@
         <v>61</v>
       </c>
       <c r="H12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" t="s">
         <v>62</v>
-      </c>
-      <c r="I12" t="s">
-        <v>54</v>
       </c>
       <c r="J12" t="s">
         <v>63</v>
@@ -3491,16 +3484,16 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>8</v>
+        <v>78303</v>
       </c>
       <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
         <v>29</v>
-      </c>
-      <c r="C13">
-        <v>78303</v>
-      </c>
-      <c r="D13" t="s">
-        <v>49</v>
       </c>
       <c r="E13" t="s">
         <v>59</v>
@@ -3512,10 +3505,10 @@
         <v>64</v>
       </c>
       <c r="H13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I13" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="J13" t="s">
         <v>63</v>
@@ -3529,16 +3522,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>8</v>
+        <v>78303</v>
       </c>
       <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
         <v>33</v>
-      </c>
-      <c r="C14">
-        <v>78303</v>
-      </c>
-      <c r="D14" t="s">
-        <v>49</v>
       </c>
       <c r="E14" t="s">
         <v>58</v>
@@ -3550,10 +3543,10 @@
         <v>64</v>
       </c>
       <c r="H14" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="J14" t="s">
         <v>63</v>
@@ -3567,16 +3560,16 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>8</v>
+        <v>78304</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C15">
-        <v>78304</v>
+        <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
@@ -3605,16 +3598,16 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>8</v>
+        <v>78304</v>
       </c>
       <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
         <v>22</v>
-      </c>
-      <c r="C16">
-        <v>78304</v>
-      </c>
-      <c r="D16" t="s">
-        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
@@ -3643,16 +3636,16 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17">
-        <v>8</v>
+        <v>78304</v>
       </c>
       <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
         <v>23</v>
-      </c>
-      <c r="C17">
-        <v>78304</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>78</v>
@@ -3681,16 +3674,16 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18">
-        <v>8</v>
+        <v>78304</v>
       </c>
       <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
         <v>29</v>
-      </c>
-      <c r="C18">
-        <v>78304</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>80</v>
@@ -3719,16 +3712,16 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19">
-        <v>8</v>
+        <v>78304</v>
       </c>
       <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
         <v>33</v>
-      </c>
-      <c r="C19">
-        <v>78304</v>
-      </c>
-      <c r="D19" t="s">
-        <v>67</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
@@ -3757,16 +3750,16 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20">
-        <v>8</v>
+        <v>78305</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="C20">
-        <v>78305</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
         <v>84</v>
@@ -3795,16 +3788,16 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21">
-        <v>8</v>
+        <v>78305</v>
       </c>
       <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
         <v>22</v>
-      </c>
-      <c r="C21">
-        <v>78305</v>
-      </c>
-      <c r="D21" t="s">
-        <v>83</v>
       </c>
       <c r="E21" t="s">
         <v>84</v>
@@ -3833,16 +3826,16 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22">
-        <v>8</v>
+        <v>78305</v>
       </c>
       <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
         <v>23</v>
-      </c>
-      <c r="C22">
-        <v>78305</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
       </c>
       <c r="E22" t="s">
         <v>92</v>
@@ -3871,16 +3864,16 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23">
-        <v>8</v>
+        <v>78306</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="C23">
-        <v>78306</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
         <v>95</v>
@@ -3909,16 +3902,16 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24">
-        <v>8</v>
+        <v>78306</v>
       </c>
       <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
         <v>22</v>
-      </c>
-      <c r="C24">
-        <v>78306</v>
-      </c>
-      <c r="D24" t="s">
-        <v>94</v>
       </c>
       <c r="E24" t="s">
         <v>95</v>
@@ -3947,16 +3940,16 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25">
-        <v>8</v>
+        <v>78306</v>
       </c>
       <c r="B25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
         <v>23</v>
-      </c>
-      <c r="C25">
-        <v>78306</v>
-      </c>
-      <c r="D25" t="s">
-        <v>94</v>
       </c>
       <c r="E25" t="s">
         <v>104</v>
@@ -3985,16 +3978,16 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26">
-        <v>8</v>
+        <v>78306</v>
       </c>
       <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
         <v>29</v>
-      </c>
-      <c r="C26">
-        <v>78306</v>
-      </c>
-      <c r="D26" t="s">
-        <v>94</v>
       </c>
       <c r="E26" t="s">
         <v>104</v>
@@ -4023,16 +4016,16 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27">
-        <v>8</v>
+        <v>78307</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C27">
-        <v>78307</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
         <v>110</v>
@@ -4061,16 +4054,16 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28">
-        <v>8</v>
+        <v>78307</v>
       </c>
       <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
         <v>22</v>
-      </c>
-      <c r="C28">
-        <v>78307</v>
-      </c>
-      <c r="D28" t="s">
-        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>110</v>
@@ -4099,16 +4092,16 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29">
-        <v>8</v>
+        <v>78307</v>
       </c>
       <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
         <v>23</v>
-      </c>
-      <c r="C29">
-        <v>78307</v>
-      </c>
-      <c r="D29" t="s">
-        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>118</v>
@@ -4120,7 +4113,7 @@
         <v>120</v>
       </c>
       <c r="H29" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I29" t="s">
         <v>114</v>
@@ -4137,28 +4130,28 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30">
-        <v>8</v>
+        <v>78307</v>
       </c>
       <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
         <v>29</v>
       </c>
-      <c r="C30">
-        <v>78307</v>
-      </c>
-      <c r="D30" t="s">
-        <v>109</v>
-      </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s">
         <v>119</v>
       </c>
       <c r="G30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H30" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I30" t="s">
         <v>114</v>
@@ -4175,19 +4168,19 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31">
-        <v>8</v>
+        <v>78307</v>
       </c>
       <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
         <v>33</v>
       </c>
-      <c r="C31">
-        <v>78307</v>
-      </c>
-      <c r="D31" t="s">
-        <v>109</v>
-      </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
         <v>124</v>
@@ -4213,22 +4206,22 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32">
-        <v>8</v>
+        <v>78307</v>
       </c>
       <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
         <v>40</v>
-      </c>
-      <c r="C32">
-        <v>78307</v>
-      </c>
-      <c r="D32" t="s">
-        <v>109</v>
       </c>
       <c r="E32" t="s">
         <v>118</v>
       </c>
       <c r="F32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G32" t="s">
         <v>125</v>
@@ -4237,7 +4230,7 @@
         <v>121</v>
       </c>
       <c r="I32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J32" t="s">
         <v>115</v>
@@ -4251,683 +4244,683 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33">
-        <v>8</v>
+        <v>78311</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="C33">
-        <v>78311</v>
+        <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34">
-        <v>8</v>
+        <v>78311</v>
       </c>
       <c r="B34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
         <v>22</v>
       </c>
-      <c r="C34">
-        <v>78311</v>
-      </c>
-      <c r="D34" t="s">
-        <v>127</v>
-      </c>
       <c r="E34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35">
-        <v>8</v>
+        <v>78311</v>
       </c>
       <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
         <v>23</v>
       </c>
-      <c r="C35">
-        <v>78311</v>
-      </c>
-      <c r="D35" t="s">
-        <v>127</v>
-      </c>
       <c r="E35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" t="s">
+        <v>141</v>
+      </c>
+      <c r="G35" t="s">
+        <v>142</v>
+      </c>
+      <c r="H35" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" t="s">
+        <v>133</v>
+      </c>
+      <c r="J35" t="s">
+        <v>134</v>
+      </c>
+      <c r="K35" t="s">
+        <v>135</v>
+      </c>
+      <c r="L35" t="s">
         <v>139</v>
-      </c>
-      <c r="F35" t="s">
-        <v>140</v>
-      </c>
-      <c r="G35" t="s">
-        <v>141</v>
-      </c>
-      <c r="H35" t="s">
-        <v>142</v>
-      </c>
-      <c r="I35" t="s">
-        <v>132</v>
-      </c>
-      <c r="J35" t="s">
-        <v>133</v>
-      </c>
-      <c r="K35" t="s">
-        <v>134</v>
-      </c>
-      <c r="L35" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36">
-        <v>8</v>
+        <v>78311</v>
       </c>
       <c r="B36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36">
+        <v>8</v>
+      </c>
+      <c r="D36" t="s">
         <v>29</v>
       </c>
-      <c r="C36">
-        <v>78311</v>
-      </c>
-      <c r="D36" t="s">
-        <v>127</v>
-      </c>
       <c r="E36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37">
-        <v>8</v>
+        <v>78311</v>
       </c>
       <c r="B37" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37">
+        <v>8</v>
+      </c>
+      <c r="D37" t="s">
         <v>33</v>
       </c>
-      <c r="C37">
-        <v>78311</v>
-      </c>
-      <c r="D37" t="s">
-        <v>127</v>
-      </c>
       <c r="E37" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" t="s">
+        <v>146</v>
+      </c>
+      <c r="G37" t="s">
+        <v>147</v>
+      </c>
+      <c r="H37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I37" t="s">
+        <v>133</v>
+      </c>
+      <c r="J37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K37" t="s">
+        <v>148</v>
+      </c>
+      <c r="L37" t="s">
         <v>144</v>
-      </c>
-      <c r="F37" t="s">
-        <v>145</v>
-      </c>
-      <c r="G37" t="s">
-        <v>146</v>
-      </c>
-      <c r="H37" t="s">
-        <v>142</v>
-      </c>
-      <c r="I37" t="s">
-        <v>132</v>
-      </c>
-      <c r="J37" t="s">
-        <v>133</v>
-      </c>
-      <c r="K37" t="s">
-        <v>147</v>
-      </c>
-      <c r="L37" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38">
-        <v>8</v>
+        <v>78311</v>
       </c>
       <c r="B38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
         <v>40</v>
       </c>
-      <c r="C38">
-        <v>78311</v>
-      </c>
-      <c r="D38" t="s">
-        <v>127</v>
-      </c>
       <c r="E38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" t="s">
+        <v>146</v>
+      </c>
+      <c r="G38" t="s">
+        <v>147</v>
+      </c>
+      <c r="H38" t="s">
+        <v>143</v>
+      </c>
+      <c r="I38" t="s">
+        <v>133</v>
+      </c>
+      <c r="J38" t="s">
+        <v>134</v>
+      </c>
+      <c r="K38" t="s">
+        <v>148</v>
+      </c>
+      <c r="L38" t="s">
         <v>144</v>
-      </c>
-      <c r="F38" t="s">
-        <v>145</v>
-      </c>
-      <c r="G38" t="s">
-        <v>146</v>
-      </c>
-      <c r="H38" t="s">
-        <v>142</v>
-      </c>
-      <c r="I38" t="s">
-        <v>132</v>
-      </c>
-      <c r="J38" t="s">
-        <v>133</v>
-      </c>
-      <c r="K38" t="s">
-        <v>147</v>
-      </c>
-      <c r="L38" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39">
-        <v>8</v>
+        <v>78313</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="C39">
-        <v>78313</v>
+        <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G39" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H39" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40">
-        <v>8</v>
+        <v>78313</v>
       </c>
       <c r="B40" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
         <v>22</v>
       </c>
-      <c r="C40">
-        <v>78313</v>
-      </c>
-      <c r="D40" t="s">
-        <v>148</v>
-      </c>
       <c r="E40" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" t="s">
+        <v>158</v>
+      </c>
+      <c r="G40" t="s">
+        <v>159</v>
+      </c>
+      <c r="H40" t="s">
+        <v>160</v>
+      </c>
+      <c r="I40" t="s">
+        <v>154</v>
+      </c>
+      <c r="J40" t="s">
+        <v>155</v>
+      </c>
+      <c r="K40" t="s">
+        <v>156</v>
+      </c>
+      <c r="L40" t="s">
         <v>157</v>
-      </c>
-      <c r="G40" t="s">
-        <v>158</v>
-      </c>
-      <c r="H40" t="s">
-        <v>159</v>
-      </c>
-      <c r="I40" t="s">
-        <v>153</v>
-      </c>
-      <c r="J40" t="s">
-        <v>154</v>
-      </c>
-      <c r="K40" t="s">
-        <v>155</v>
-      </c>
-      <c r="L40" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41">
-        <v>8</v>
+        <v>78313</v>
       </c>
       <c r="B41" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
         <v>23</v>
       </c>
-      <c r="C41">
-        <v>78313</v>
-      </c>
-      <c r="D41" t="s">
-        <v>148</v>
-      </c>
       <c r="E41" t="s">
+        <v>161</v>
+      </c>
+      <c r="F41" t="s">
+        <v>162</v>
+      </c>
+      <c r="G41" t="s">
+        <v>159</v>
+      </c>
+      <c r="H41" t="s">
         <v>160</v>
       </c>
-      <c r="F41" t="s">
-        <v>161</v>
-      </c>
-      <c r="G41" t="s">
-        <v>158</v>
-      </c>
-      <c r="H41" t="s">
-        <v>159</v>
-      </c>
       <c r="I41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42">
-        <v>8</v>
+        <v>78313</v>
       </c>
       <c r="B42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
         <v>29</v>
       </c>
-      <c r="C42">
-        <v>78313</v>
-      </c>
-      <c r="D42" t="s">
-        <v>148</v>
-      </c>
       <c r="E42" t="s">
+        <v>161</v>
+      </c>
+      <c r="F42" t="s">
+        <v>162</v>
+      </c>
+      <c r="G42" t="s">
+        <v>163</v>
+      </c>
+      <c r="H42" t="s">
         <v>160</v>
       </c>
-      <c r="F42" t="s">
-        <v>161</v>
-      </c>
-      <c r="G42" t="s">
-        <v>162</v>
-      </c>
-      <c r="H42" t="s">
-        <v>159</v>
-      </c>
       <c r="I42" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="C43">
-        <v>78318</v>
+        <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>163</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F43" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I43" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K43" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B44" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
         <v>22</v>
       </c>
-      <c r="C44">
-        <v>78318</v>
-      </c>
-      <c r="D44" t="s">
-        <v>163</v>
-      </c>
       <c r="E44" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G44" t="s">
+        <v>173</v>
+      </c>
+      <c r="H44" t="s">
+        <v>168</v>
+      </c>
+      <c r="I44" t="s">
+        <v>169</v>
+      </c>
+      <c r="J44" t="s">
+        <v>170</v>
+      </c>
+      <c r="K44" t="s">
+        <v>171</v>
+      </c>
+      <c r="L44" t="s">
         <v>172</v>
-      </c>
-      <c r="H44" t="s">
-        <v>167</v>
-      </c>
-      <c r="I44" t="s">
-        <v>168</v>
-      </c>
-      <c r="J44" t="s">
-        <v>169</v>
-      </c>
-      <c r="K44" t="s">
-        <v>170</v>
-      </c>
-      <c r="L44" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B45" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
         <v>23</v>
       </c>
-      <c r="C45">
-        <v>78318</v>
-      </c>
-      <c r="D45" t="s">
-        <v>163</v>
-      </c>
       <c r="E45" t="s">
+        <v>174</v>
+      </c>
+      <c r="F45" t="s">
+        <v>175</v>
+      </c>
+      <c r="G45" t="s">
         <v>173</v>
       </c>
-      <c r="F45" t="s">
-        <v>174</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
+        <v>176</v>
+      </c>
+      <c r="I45" t="s">
+        <v>169</v>
+      </c>
+      <c r="J45" t="s">
+        <v>170</v>
+      </c>
+      <c r="K45" t="s">
+        <v>177</v>
+      </c>
+      <c r="L45" t="s">
         <v>172</v>
-      </c>
-      <c r="H45" t="s">
-        <v>175</v>
-      </c>
-      <c r="I45" t="s">
-        <v>168</v>
-      </c>
-      <c r="J45" t="s">
-        <v>169</v>
-      </c>
-      <c r="K45" t="s">
-        <v>176</v>
-      </c>
-      <c r="L45" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B46" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
         <v>29</v>
       </c>
-      <c r="C46">
-        <v>78318</v>
-      </c>
-      <c r="D46" t="s">
-        <v>163</v>
-      </c>
       <c r="E46" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G46" t="s">
+        <v>178</v>
+      </c>
+      <c r="H46" t="s">
+        <v>176</v>
+      </c>
+      <c r="I46" t="s">
+        <v>169</v>
+      </c>
+      <c r="J46" t="s">
+        <v>170</v>
+      </c>
+      <c r="K46" t="s">
         <v>177</v>
       </c>
-      <c r="H46" t="s">
-        <v>175</v>
-      </c>
-      <c r="I46" t="s">
-        <v>168</v>
-      </c>
-      <c r="J46" t="s">
-        <v>169</v>
-      </c>
-      <c r="K46" t="s">
-        <v>176</v>
-      </c>
       <c r="L46" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B47" t="s">
+        <v>164</v>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+      <c r="D47" t="s">
         <v>33</v>
       </c>
-      <c r="C47">
-        <v>78318</v>
-      </c>
-      <c r="D47" t="s">
-        <v>163</v>
-      </c>
       <c r="E47" t="s">
+        <v>179</v>
+      </c>
+      <c r="F47" t="s">
+        <v>180</v>
+      </c>
+      <c r="G47" t="s">
         <v>178</v>
       </c>
-      <c r="F47" t="s">
-        <v>179</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
+        <v>181</v>
+      </c>
+      <c r="I47" t="s">
+        <v>169</v>
+      </c>
+      <c r="J47" t="s">
+        <v>170</v>
+      </c>
+      <c r="K47" t="s">
         <v>177</v>
       </c>
-      <c r="H47" t="s">
-        <v>180</v>
-      </c>
-      <c r="I47" t="s">
-        <v>168</v>
-      </c>
-      <c r="J47" t="s">
-        <v>169</v>
-      </c>
-      <c r="K47" t="s">
-        <v>176</v>
-      </c>
       <c r="L47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B48" t="s">
+        <v>164</v>
+      </c>
+      <c r="C48">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
         <v>40</v>
       </c>
-      <c r="C48">
-        <v>78318</v>
-      </c>
-      <c r="D48" t="s">
-        <v>163</v>
-      </c>
       <c r="E48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H48" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J48" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K48" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B49" t="s">
+        <v>164</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
         <v>41</v>
       </c>
-      <c r="C49">
-        <v>78318</v>
-      </c>
-      <c r="D49" t="s">
-        <v>163</v>
-      </c>
       <c r="E49" t="s">
+        <v>185</v>
+      </c>
+      <c r="F49" t="s">
+        <v>182</v>
+      </c>
+      <c r="G49" t="s">
+        <v>183</v>
+      </c>
+      <c r="H49" t="s">
+        <v>176</v>
+      </c>
+      <c r="I49" t="s">
+        <v>186</v>
+      </c>
+      <c r="J49" t="s">
         <v>184</v>
       </c>
-      <c r="F49" t="s">
-        <v>181</v>
-      </c>
-      <c r="G49" t="s">
-        <v>182</v>
-      </c>
-      <c r="H49" t="s">
-        <v>175</v>
-      </c>
-      <c r="I49" t="s">
-        <v>185</v>
-      </c>
-      <c r="J49" t="s">
-        <v>183</v>
-      </c>
       <c r="K49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B50" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50">
+        <v>8</v>
+      </c>
+      <c r="D50" t="s">
         <v>46</v>
       </c>
-      <c r="C50">
-        <v>78318</v>
-      </c>
-      <c r="D50" t="s">
-        <v>163</v>
-      </c>
       <c r="E50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G50" t="s">
         <v>187</v>
       </c>
       <c r="H50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L50" t="s">
         <v>188</v>
@@ -4935,16 +4928,16 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B51" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51">
+        <v>8</v>
+      </c>
+      <c r="D51" t="s">
         <v>189</v>
-      </c>
-      <c r="C51">
-        <v>78318</v>
-      </c>
-      <c r="D51" t="s">
-        <v>163</v>
       </c>
       <c r="E51" t="s">
         <v>190</v>
@@ -4956,13 +4949,13 @@
         <v>187</v>
       </c>
       <c r="H51" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J51" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K51" t="s">
         <v>192</v>
@@ -4973,16 +4966,16 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
         <v>193</v>
-      </c>
-      <c r="C52">
-        <v>78318</v>
-      </c>
-      <c r="D52" t="s">
-        <v>163</v>
       </c>
       <c r="E52" t="s">
         <v>194</v>
@@ -4994,10 +4987,10 @@
         <v>196</v>
       </c>
       <c r="H52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J52" t="s">
         <v>197</v>
@@ -5011,16 +5004,16 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
         <v>198</v>
-      </c>
-      <c r="C53">
-        <v>78318</v>
-      </c>
-      <c r="D53" t="s">
-        <v>163</v>
       </c>
       <c r="E53" t="s">
         <v>194</v>
@@ -5035,13 +5028,13 @@
         <v>199</v>
       </c>
       <c r="I53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J53" t="s">
         <v>197</v>
       </c>
       <c r="K53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L53" t="s">
         <v>188</v>
@@ -5049,16 +5042,16 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B54" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54">
+        <v>8</v>
+      </c>
+      <c r="D54" t="s">
         <v>200</v>
-      </c>
-      <c r="C54">
-        <v>78318</v>
-      </c>
-      <c r="D54" t="s">
-        <v>163</v>
       </c>
       <c r="E54" t="s">
         <v>201</v>
@@ -5073,13 +5066,13 @@
         <v>199</v>
       </c>
       <c r="I54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J54" t="s">
         <v>197</v>
       </c>
       <c r="K54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L54" t="s">
         <v>188</v>
@@ -5087,16 +5080,16 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55">
+        <v>8</v>
+      </c>
+      <c r="D55" t="s">
         <v>203</v>
-      </c>
-      <c r="C55">
-        <v>78318</v>
-      </c>
-      <c r="D55" t="s">
-        <v>163</v>
       </c>
       <c r="E55" t="s">
         <v>201</v>
@@ -5111,13 +5104,13 @@
         <v>199</v>
       </c>
       <c r="I55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J55" t="s">
         <v>197</v>
       </c>
       <c r="K55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L55" t="s">
         <v>188</v>
@@ -5125,16 +5118,16 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56">
-        <v>8</v>
+        <v>78318</v>
       </c>
       <c r="B56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56">
+        <v>8</v>
+      </c>
+      <c r="D56" t="s">
         <v>205</v>
-      </c>
-      <c r="C56">
-        <v>78318</v>
-      </c>
-      <c r="D56" t="s">
-        <v>163</v>
       </c>
       <c r="E56" t="s">
         <v>190</v>
@@ -5155,7 +5148,7 @@
         <v>197</v>
       </c>
       <c r="K56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L56" t="s">
         <v>188</v>
@@ -5163,16 +5156,16 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>208</v>
       </c>
       <c r="C57">
-        <v>78319</v>
+        <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>208</v>
+        <v>13</v>
       </c>
       <c r="E57" t="s">
         <v>209</v>
@@ -5201,16 +5194,16 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B58" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
         <v>22</v>
-      </c>
-      <c r="C58">
-        <v>78319</v>
-      </c>
-      <c r="D58" t="s">
-        <v>208</v>
       </c>
       <c r="E58" t="s">
         <v>209</v>
@@ -5239,16 +5232,16 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B59" t="s">
+        <v>208</v>
+      </c>
+      <c r="C59">
+        <v>8</v>
+      </c>
+      <c r="D59" t="s">
         <v>23</v>
-      </c>
-      <c r="C59">
-        <v>78319</v>
-      </c>
-      <c r="D59" t="s">
-        <v>208</v>
       </c>
       <c r="E59" t="s">
         <v>218</v>
@@ -5277,16 +5270,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B60" t="s">
+        <v>208</v>
+      </c>
+      <c r="C60">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
         <v>29</v>
-      </c>
-      <c r="C60">
-        <v>78319</v>
-      </c>
-      <c r="D60" t="s">
-        <v>208</v>
       </c>
       <c r="E60" t="s">
         <v>218</v>
@@ -5315,16 +5308,16 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B61" t="s">
+        <v>208</v>
+      </c>
+      <c r="C61">
+        <v>8</v>
+      </c>
+      <c r="D61" t="s">
         <v>33</v>
-      </c>
-      <c r="C61">
-        <v>78319</v>
-      </c>
-      <c r="D61" t="s">
-        <v>208</v>
       </c>
       <c r="E61" t="s">
         <v>221</v>
@@ -5353,16 +5346,16 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B62" t="s">
+        <v>208</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62" t="s">
         <v>40</v>
-      </c>
-      <c r="C62">
-        <v>78319</v>
-      </c>
-      <c r="D62" t="s">
-        <v>208</v>
       </c>
       <c r="E62" t="s">
         <v>221</v>
@@ -5391,16 +5384,16 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B63" t="s">
+        <v>208</v>
+      </c>
+      <c r="C63">
+        <v>8</v>
+      </c>
+      <c r="D63" t="s">
         <v>41</v>
-      </c>
-      <c r="C63">
-        <v>78319</v>
-      </c>
-      <c r="D63" t="s">
-        <v>208</v>
       </c>
       <c r="E63" t="s">
         <v>224</v>
@@ -5429,16 +5422,16 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B64" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64">
+        <v>8</v>
+      </c>
+      <c r="D64" t="s">
         <v>46</v>
-      </c>
-      <c r="C64">
-        <v>78319</v>
-      </c>
-      <c r="D64" t="s">
-        <v>208</v>
       </c>
       <c r="E64" t="s">
         <v>224</v>
@@ -5467,16 +5460,16 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B65" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65">
+        <v>8</v>
+      </c>
+      <c r="D65" t="s">
         <v>189</v>
-      </c>
-      <c r="C65">
-        <v>78319</v>
-      </c>
-      <c r="D65" t="s">
-        <v>208</v>
       </c>
       <c r="E65" t="s">
         <v>232</v>
@@ -5505,16 +5498,16 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B66" t="s">
+        <v>208</v>
+      </c>
+      <c r="C66">
+        <v>8</v>
+      </c>
+      <c r="D66" t="s">
         <v>193</v>
-      </c>
-      <c r="C66">
-        <v>78319</v>
-      </c>
-      <c r="D66" t="s">
-        <v>208</v>
       </c>
       <c r="E66" t="s">
         <v>232</v>
@@ -5543,16 +5536,16 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B67" t="s">
+        <v>208</v>
+      </c>
+      <c r="C67">
+        <v>8</v>
+      </c>
+      <c r="D67" t="s">
         <v>198</v>
-      </c>
-      <c r="C67">
-        <v>78319</v>
-      </c>
-      <c r="D67" t="s">
-        <v>208</v>
       </c>
       <c r="E67" t="s">
         <v>238</v>
@@ -5581,22 +5574,22 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B68" t="s">
+        <v>208</v>
+      </c>
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
         <v>200</v>
-      </c>
-      <c r="C68">
-        <v>78319</v>
-      </c>
-      <c r="D68" t="s">
-        <v>208</v>
       </c>
       <c r="E68" t="s">
         <v>238</v>
       </c>
       <c r="F68" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G68" t="s">
         <v>240</v>
@@ -5614,978 +5607,992 @@
         <v>230</v>
       </c>
       <c r="L68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B69" t="s">
+        <v>208</v>
+      </c>
+      <c r="C69">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
         <v>203</v>
       </c>
-      <c r="C69">
-        <v>78319</v>
-      </c>
-      <c r="D69" t="s">
-        <v>208</v>
-      </c>
       <c r="E69" t="s">
+        <v>242</v>
+      </c>
+      <c r="F69" t="s">
         <v>243</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>244</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>245</v>
       </c>
-      <c r="H69" t="s">
+      <c r="I69" t="s">
         <v>246</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>247</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>248</v>
       </c>
-      <c r="K69" t="s">
-        <v>249</v>
-      </c>
       <c r="L69" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B70" t="s">
+        <v>208</v>
+      </c>
+      <c r="C70">
+        <v>8</v>
+      </c>
+      <c r="D70" t="s">
         <v>205</v>
       </c>
-      <c r="C70">
-        <v>78319</v>
-      </c>
-      <c r="D70" t="s">
-        <v>208</v>
-      </c>
       <c r="E70" t="s">
+        <v>242</v>
+      </c>
+      <c r="F70" t="s">
         <v>243</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>244</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>245</v>
       </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>246</v>
       </c>
-      <c r="I70" t="s">
+      <c r="J70" t="s">
         <v>247</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>248</v>
       </c>
-      <c r="K70" t="s">
-        <v>249</v>
-      </c>
       <c r="L70" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B71" t="s">
+        <v>208</v>
+      </c>
+      <c r="C71">
+        <v>8</v>
+      </c>
+      <c r="D71" t="s">
+        <v>249</v>
+      </c>
+      <c r="E71" t="s">
         <v>250</v>
       </c>
-      <c r="C71">
-        <v>78319</v>
-      </c>
-      <c r="D71" t="s">
-        <v>208</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>251</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>252</v>
       </c>
-      <c r="G71" t="s">
-        <v>253</v>
-      </c>
       <c r="H71" t="s">
+        <v>245</v>
+      </c>
+      <c r="I71" t="s">
         <v>246</v>
       </c>
-      <c r="I71" t="s">
+      <c r="J71" t="s">
         <v>247</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>248</v>
       </c>
-      <c r="K71" t="s">
-        <v>249</v>
-      </c>
       <c r="L71" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C72">
+        <v>8</v>
+      </c>
+      <c r="D72" t="s">
+        <v>253</v>
+      </c>
+      <c r="E72" t="s">
+        <v>250</v>
+      </c>
+      <c r="F72" t="s">
+        <v>251</v>
+      </c>
+      <c r="G72" t="s">
+        <v>252</v>
+      </c>
+      <c r="H72" t="s">
         <v>254</v>
       </c>
-      <c r="C72">
-        <v>78319</v>
-      </c>
-      <c r="D72" t="s">
-        <v>208</v>
-      </c>
-      <c r="E72" t="s">
-        <v>251</v>
-      </c>
-      <c r="F72" t="s">
-        <v>252</v>
-      </c>
-      <c r="G72" t="s">
-        <v>253</v>
-      </c>
-      <c r="H72" t="s">
-        <v>255</v>
-      </c>
       <c r="I72" t="s">
+        <v>246</v>
+      </c>
+      <c r="J72" t="s">
         <v>247</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>248</v>
       </c>
-      <c r="K72" t="s">
-        <v>249</v>
-      </c>
       <c r="L72" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73">
+        <v>8</v>
+      </c>
+      <c r="D73" t="s">
+        <v>255</v>
+      </c>
+      <c r="E73" t="s">
         <v>256</v>
       </c>
-      <c r="C73">
-        <v>78319</v>
-      </c>
-      <c r="D73" t="s">
-        <v>208</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>257</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>258</v>
       </c>
-      <c r="G73" t="s">
-        <v>259</v>
-      </c>
       <c r="H73" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I73" t="s">
+        <v>246</v>
+      </c>
+      <c r="J73" t="s">
         <v>247</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>248</v>
       </c>
-      <c r="K73" t="s">
-        <v>249</v>
-      </c>
       <c r="L73" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74">
-        <v>8</v>
+        <v>78319</v>
       </c>
       <c r="B74" t="s">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="C74">
-        <v>78319</v>
+        <v>8</v>
       </c>
       <c r="D74" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="E74" t="s">
+        <v>256</v>
+      </c>
+      <c r="F74" t="s">
         <v>257</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>258</v>
       </c>
-      <c r="G74" t="s">
-        <v>259</v>
-      </c>
       <c r="H74" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I74" t="s">
+        <v>246</v>
+      </c>
+      <c r="J74" t="s">
         <v>247</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>248</v>
       </c>
-      <c r="K74" t="s">
-        <v>249</v>
-      </c>
       <c r="L74" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B75" t="s">
-        <v>12</v>
+        <v>260</v>
       </c>
       <c r="C75">
-        <v>78320</v>
+        <v>8</v>
       </c>
       <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
         <v>261</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>262</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>263</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>264</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>265</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>266</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>267</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>268</v>
-      </c>
-      <c r="L75" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B76" t="s">
+        <v>260</v>
+      </c>
+      <c r="C76">
+        <v>8</v>
+      </c>
+      <c r="D76" t="s">
         <v>22</v>
       </c>
-      <c r="C76">
-        <v>78320</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>261</v>
       </c>
-      <c r="E76" t="s">
-        <v>262</v>
-      </c>
       <c r="F76" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G76" t="s">
+        <v>263</v>
+      </c>
+      <c r="H76" t="s">
         <v>264</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>265</v>
       </c>
-      <c r="I76" t="s">
+      <c r="J76" t="s">
         <v>266</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>267</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" t="s">
         <v>268</v>
-      </c>
-      <c r="L76" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B77" t="s">
+        <v>260</v>
+      </c>
+      <c r="C77">
+        <v>8</v>
+      </c>
+      <c r="D77" t="s">
         <v>23</v>
       </c>
-      <c r="C77">
-        <v>78320</v>
-      </c>
-      <c r="D77" t="s">
-        <v>261</v>
-      </c>
       <c r="E77" t="s">
+        <v>270</v>
+      </c>
+      <c r="F77" t="s">
         <v>271</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>272</v>
       </c>
-      <c r="G77" t="s">
-        <v>273</v>
-      </c>
       <c r="H77" t="s">
+        <v>264</v>
+      </c>
+      <c r="I77" t="s">
         <v>265</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>266</v>
       </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>267</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" t="s">
         <v>268</v>
-      </c>
-      <c r="L77" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B78" t="s">
+        <v>260</v>
+      </c>
+      <c r="C78">
+        <v>8</v>
+      </c>
+      <c r="D78" t="s">
         <v>29</v>
       </c>
-      <c r="C78">
-        <v>78320</v>
-      </c>
-      <c r="D78" t="s">
-        <v>261</v>
-      </c>
       <c r="E78" t="s">
+        <v>270</v>
+      </c>
+      <c r="F78" t="s">
         <v>271</v>
       </c>
-      <c r="F78" t="s">
-        <v>272</v>
-      </c>
       <c r="G78" t="s">
+        <v>273</v>
+      </c>
+      <c r="H78" t="s">
+        <v>264</v>
+      </c>
+      <c r="I78" t="s">
         <v>274</v>
       </c>
-      <c r="H78" t="s">
-        <v>265</v>
-      </c>
-      <c r="I78" t="s">
-        <v>275</v>
-      </c>
       <c r="J78" t="s">
+        <v>266</v>
+      </c>
+      <c r="K78" t="s">
         <v>267</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
         <v>268</v>
-      </c>
-      <c r="L78" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B79" t="s">
+        <v>260</v>
+      </c>
+      <c r="C79">
+        <v>8</v>
+      </c>
+      <c r="D79" t="s">
         <v>33</v>
       </c>
-      <c r="C79">
-        <v>78320</v>
-      </c>
-      <c r="D79" t="s">
-        <v>261</v>
-      </c>
       <c r="E79" t="s">
+        <v>275</v>
+      </c>
+      <c r="F79" t="s">
         <v>276</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
+        <v>273</v>
+      </c>
+      <c r="H79" t="s">
         <v>277</v>
       </c>
-      <c r="G79" t="s">
-        <v>274</v>
-      </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
+        <v>265</v>
+      </c>
+      <c r="J79" t="s">
         <v>278</v>
       </c>
-      <c r="I79" t="s">
-        <v>266</v>
-      </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>279</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
         <v>280</v>
-      </c>
-      <c r="L79" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B80" t="s">
+        <v>260</v>
+      </c>
+      <c r="C80">
+        <v>8</v>
+      </c>
+      <c r="D80" t="s">
         <v>40</v>
       </c>
-      <c r="C80">
-        <v>78320</v>
-      </c>
-      <c r="D80" t="s">
-        <v>261</v>
-      </c>
       <c r="E80" t="s">
+        <v>281</v>
+      </c>
+      <c r="F80" t="s">
+        <v>276</v>
+      </c>
+      <c r="G80" t="s">
         <v>282</v>
       </c>
-      <c r="F80" t="s">
+      <c r="H80" t="s">
         <v>277</v>
       </c>
-      <c r="G80" t="s">
+      <c r="I80" t="s">
         <v>283</v>
       </c>
-      <c r="H80" t="s">
-        <v>278</v>
-      </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>284</v>
       </c>
-      <c r="J80" t="s">
-        <v>285</v>
-      </c>
       <c r="K80" t="s">
+        <v>279</v>
+      </c>
+      <c r="L80" t="s">
         <v>280</v>
-      </c>
-      <c r="L80" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B81" t="s">
+        <v>260</v>
+      </c>
+      <c r="C81">
+        <v>8</v>
+      </c>
+      <c r="D81" t="s">
         <v>41</v>
       </c>
-      <c r="C81">
-        <v>78320</v>
-      </c>
-      <c r="D81" t="s">
-        <v>261</v>
-      </c>
       <c r="E81" t="s">
+        <v>281</v>
+      </c>
+      <c r="F81" t="s">
+        <v>269</v>
+      </c>
+      <c r="G81" t="s">
         <v>282</v>
       </c>
-      <c r="F81" t="s">
-        <v>270</v>
-      </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
+        <v>277</v>
+      </c>
+      <c r="I81" t="s">
         <v>283</v>
       </c>
-      <c r="H81" t="s">
-        <v>278</v>
-      </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>284</v>
       </c>
-      <c r="J81" t="s">
-        <v>285</v>
-      </c>
       <c r="K81" t="s">
+        <v>279</v>
+      </c>
+      <c r="L81" t="s">
         <v>280</v>
-      </c>
-      <c r="L81" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B82" t="s">
+        <v>260</v>
+      </c>
+      <c r="C82">
+        <v>8</v>
+      </c>
+      <c r="D82" t="s">
         <v>46</v>
       </c>
-      <c r="C82">
-        <v>78320</v>
-      </c>
-      <c r="D82" t="s">
-        <v>261</v>
-      </c>
       <c r="E82" t="s">
+        <v>285</v>
+      </c>
+      <c r="F82" t="s">
         <v>286</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>287</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>288</v>
       </c>
-      <c r="H82" t="s">
-        <v>289</v>
-      </c>
       <c r="I82" t="s">
+        <v>283</v>
+      </c>
+      <c r="J82" t="s">
         <v>284</v>
       </c>
-      <c r="J82" t="s">
-        <v>285</v>
-      </c>
       <c r="K82" t="s">
+        <v>279</v>
+      </c>
+      <c r="L82" t="s">
         <v>280</v>
-      </c>
-      <c r="L82" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B83" t="s">
+        <v>260</v>
+      </c>
+      <c r="C83">
+        <v>8</v>
+      </c>
+      <c r="D83" t="s">
         <v>189</v>
       </c>
-      <c r="C83">
-        <v>78320</v>
-      </c>
-      <c r="D83" t="s">
-        <v>261</v>
-      </c>
       <c r="E83" t="s">
+        <v>285</v>
+      </c>
+      <c r="F83" t="s">
         <v>286</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>287</v>
       </c>
-      <c r="G83" t="s">
-        <v>288</v>
-      </c>
       <c r="H83" t="s">
+        <v>289</v>
+      </c>
+      <c r="I83" t="s">
+        <v>283</v>
+      </c>
+      <c r="J83" t="s">
+        <v>284</v>
+      </c>
+      <c r="K83" t="s">
         <v>290</v>
       </c>
-      <c r="I83" t="s">
-        <v>284</v>
-      </c>
-      <c r="J83" t="s">
-        <v>285</v>
-      </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>291</v>
-      </c>
-      <c r="L83" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B84" t="s">
+        <v>260</v>
+      </c>
+      <c r="C84">
+        <v>8</v>
+      </c>
+      <c r="D84" t="s">
         <v>193</v>
       </c>
-      <c r="C84">
-        <v>78320</v>
-      </c>
-      <c r="D84" t="s">
-        <v>261</v>
-      </c>
       <c r="E84" t="s">
+        <v>292</v>
+      </c>
+      <c r="F84" t="s">
         <v>293</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>294</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>295</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>296</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>297</v>
       </c>
-      <c r="J84" t="s">
-        <v>298</v>
-      </c>
       <c r="K84" t="s">
+        <v>290</v>
+      </c>
+      <c r="L84" t="s">
         <v>291</v>
-      </c>
-      <c r="L84" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B85" t="s">
+        <v>260</v>
+      </c>
+      <c r="C85">
+        <v>8</v>
+      </c>
+      <c r="D85" t="s">
         <v>198</v>
       </c>
-      <c r="C85">
-        <v>78320</v>
-      </c>
-      <c r="D85" t="s">
-        <v>261</v>
-      </c>
       <c r="E85" t="s">
+        <v>292</v>
+      </c>
+      <c r="F85" t="s">
         <v>293</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>294</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>295</v>
       </c>
-      <c r="H85" t="s">
+      <c r="I85" t="s">
         <v>296</v>
       </c>
-      <c r="I85" t="s">
+      <c r="J85" t="s">
         <v>297</v>
       </c>
-      <c r="J85" t="s">
-        <v>298</v>
-      </c>
       <c r="K85" t="s">
+        <v>290</v>
+      </c>
+      <c r="L85" t="s">
         <v>291</v>
-      </c>
-      <c r="L85" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B86" t="s">
+        <v>260</v>
+      </c>
+      <c r="C86">
+        <v>8</v>
+      </c>
+      <c r="D86" t="s">
         <v>200</v>
       </c>
-      <c r="C86">
-        <v>78320</v>
-      </c>
-      <c r="D86" t="s">
-        <v>261</v>
-      </c>
       <c r="E86" t="s">
+        <v>298</v>
+      </c>
+      <c r="F86" t="s">
         <v>299</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>300</v>
       </c>
-      <c r="G86" t="s">
-        <v>301</v>
-      </c>
       <c r="H86" t="s">
+        <v>295</v>
+      </c>
+      <c r="I86" t="s">
         <v>296</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>297</v>
       </c>
-      <c r="J86" t="s">
-        <v>298</v>
-      </c>
       <c r="K86" t="s">
+        <v>290</v>
+      </c>
+      <c r="L86" t="s">
         <v>291</v>
-      </c>
-      <c r="L86" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87">
-        <v>8</v>
+        <v>78320</v>
       </c>
       <c r="B87" t="s">
+        <v>260</v>
+      </c>
+      <c r="C87">
+        <v>8</v>
+      </c>
+      <c r="D87" t="s">
         <v>203</v>
       </c>
-      <c r="C87">
-        <v>78320</v>
-      </c>
-      <c r="D87" t="s">
-        <v>261</v>
-      </c>
       <c r="E87" t="s">
+        <v>298</v>
+      </c>
+      <c r="F87" t="s">
         <v>299</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>300</v>
       </c>
-      <c r="G87" t="s">
-        <v>302</v>
-      </c>
       <c r="H87" t="s">
+        <v>295</v>
+      </c>
+      <c r="I87" t="s">
         <v>296</v>
       </c>
-      <c r="I87" t="s">
+      <c r="J87" t="s">
         <v>297</v>
       </c>
-      <c r="J87" t="s">
-        <v>298</v>
-      </c>
       <c r="K87" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>301</v>
       </c>
       <c r="C88">
-        <v>78321</v>
+        <v>8</v>
       </c>
       <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>302</v>
+      </c>
+      <c r="F88" t="s">
         <v>303</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>304</v>
       </c>
-      <c r="F88" t="s">
+      <c r="H88" t="s">
         <v>305</v>
       </c>
-      <c r="G88" t="s">
+      <c r="I88" t="s">
         <v>306</v>
       </c>
-      <c r="H88"/>
-      <c r="I88" t="s">
+      <c r="J88" t="s">
         <v>307</v>
       </c>
-      <c r="J88" t="s">
+      <c r="K88" t="s">
         <v>308</v>
       </c>
-      <c r="K88" t="s">
+      <c r="L88" t="s">
         <v>309</v>
-      </c>
-      <c r="L88" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B89" t="s">
+        <v>301</v>
+      </c>
+      <c r="C89">
+        <v>8</v>
+      </c>
+      <c r="D89" t="s">
         <v>22</v>
       </c>
-      <c r="C89">
-        <v>78321</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
+        <v>302</v>
+      </c>
+      <c r="F89" t="s">
         <v>303</v>
       </c>
-      <c r="E89" t="s">
+      <c r="G89" t="s">
         <v>304</v>
       </c>
-      <c r="F89" t="s">
+      <c r="H89" t="s">
         <v>305</v>
       </c>
-      <c r="G89" t="s">
+      <c r="I89" t="s">
         <v>306</v>
       </c>
-      <c r="H89"/>
-      <c r="I89" t="s">
+      <c r="J89" t="s">
         <v>307</v>
       </c>
-      <c r="J89" t="s">
+      <c r="K89" t="s">
         <v>308</v>
       </c>
-      <c r="K89" t="s">
-        <v>309</v>
-      </c>
       <c r="L89" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B90" t="s">
+        <v>301</v>
+      </c>
+      <c r="C90">
+        <v>8</v>
+      </c>
+      <c r="D90" t="s">
         <v>23</v>
       </c>
-      <c r="C90">
-        <v>78321</v>
-      </c>
-      <c r="D90" t="s">
-        <v>303</v>
-      </c>
       <c r="E90" t="s">
+        <v>311</v>
+      </c>
+      <c r="F90" t="s">
         <v>312</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>313</v>
       </c>
-      <c r="G90" t="s">
-        <v>314</v>
-      </c>
-      <c r="H90"/>
+      <c r="H90" t="s">
+        <v>305</v>
+      </c>
       <c r="I90" t="s">
+        <v>306</v>
+      </c>
+      <c r="J90" t="s">
         <v>307</v>
       </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
         <v>308</v>
       </c>
-      <c r="K90" t="s">
-        <v>315</v>
-      </c>
       <c r="L90" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B91" t="s">
+        <v>301</v>
+      </c>
+      <c r="C91">
+        <v>8</v>
+      </c>
+      <c r="D91" t="s">
         <v>29</v>
       </c>
-      <c r="C91">
-        <v>78321</v>
-      </c>
-      <c r="D91" t="s">
-        <v>303</v>
-      </c>
       <c r="E91" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F91" t="s">
+        <v>312</v>
+      </c>
+      <c r="G91" t="s">
         <v>313</v>
       </c>
-      <c r="G91" t="s">
-        <v>314</v>
-      </c>
-      <c r="H91"/>
+      <c r="H91" t="s">
+        <v>305</v>
+      </c>
       <c r="I91" t="s">
+        <v>306</v>
+      </c>
+      <c r="J91" t="s">
         <v>307</v>
-      </c>
-      <c r="J91" t="s">
-        <v>308</v>
       </c>
       <c r="K91" t="s">
         <v>315</v>
       </c>
       <c r="L91" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B92" t="s">
+        <v>301</v>
+      </c>
+      <c r="C92">
+        <v>8</v>
+      </c>
+      <c r="D92" t="s">
         <v>33</v>
       </c>
-      <c r="C92">
-        <v>78321</v>
-      </c>
-      <c r="D92" t="s">
-        <v>303</v>
-      </c>
       <c r="E92" t="s">
+        <v>316</v>
+      </c>
+      <c r="F92" t="s">
         <v>317</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>318</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>319</v>
       </c>
-      <c r="H92"/>
       <c r="I92" t="s">
+        <v>306</v>
+      </c>
+      <c r="J92" t="s">
         <v>307</v>
-      </c>
-      <c r="J92" t="s">
-        <v>308</v>
       </c>
       <c r="K92" t="s">
         <v>315</v>
       </c>
       <c r="L92" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B93" t="s">
+        <v>301</v>
+      </c>
+      <c r="C93">
+        <v>8</v>
+      </c>
+      <c r="D93" t="s">
         <v>40</v>
       </c>
-      <c r="C93">
-        <v>78321</v>
-      </c>
-      <c r="D93" t="s">
-        <v>303</v>
-      </c>
       <c r="E93" t="s">
+        <v>316</v>
+      </c>
+      <c r="F93" t="s">
         <v>317</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>318</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>319</v>
       </c>
-      <c r="H93"/>
       <c r="I93" t="s">
+        <v>306</v>
+      </c>
+      <c r="J93" t="s">
         <v>307</v>
       </c>
-      <c r="J93" t="s">
-        <v>320</v>
-      </c>
       <c r="K93" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="L93" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B94" t="s">
+        <v>301</v>
+      </c>
+      <c r="C94">
+        <v>8</v>
+      </c>
+      <c r="D94" t="s">
         <v>41</v>
       </c>
-      <c r="C94">
-        <v>78321</v>
-      </c>
-      <c r="D94" t="s">
-        <v>303</v>
-      </c>
       <c r="E94" t="s">
+        <v>320</v>
+      </c>
+      <c r="F94" t="s">
+        <v>321</v>
+      </c>
+      <c r="G94" t="s">
         <v>322</v>
       </c>
-      <c r="F94" t="s">
+      <c r="H94" t="s">
         <v>323</v>
       </c>
-      <c r="G94" t="s">
+      <c r="I94" t="s">
         <v>324</v>
       </c>
-      <c r="H94"/>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>325</v>
       </c>
-      <c r="J94" t="s">
-        <v>320</v>
-      </c>
       <c r="K94" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="L94" t="s">
         <v>326</v>
@@ -6593,35 +6600,37 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B95" t="s">
+        <v>301</v>
+      </c>
+      <c r="C95">
+        <v>8</v>
+      </c>
+      <c r="D95" t="s">
         <v>46</v>
       </c>
-      <c r="C95">
-        <v>78321</v>
-      </c>
-      <c r="D95" t="s">
-        <v>303</v>
-      </c>
       <c r="E95" t="s">
-        <v>327</v>
+        <v>131</v>
       </c>
       <c r="F95" t="s">
+        <v>321</v>
+      </c>
+      <c r="G95" t="s">
+        <v>322</v>
+      </c>
+      <c r="H95" t="s">
         <v>323</v>
       </c>
-      <c r="G95" t="s">
+      <c r="I95" t="s">
         <v>324</v>
       </c>
-      <c r="H95"/>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>325</v>
       </c>
-      <c r="J95" t="s">
-        <v>320</v>
-      </c>
       <c r="K95" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="L95" t="s">
         <v>326</v>
@@ -6629,35 +6638,37 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B96" t="s">
+        <v>301</v>
+      </c>
+      <c r="C96">
+        <v>8</v>
+      </c>
+      <c r="D96" t="s">
         <v>189</v>
       </c>
-      <c r="C96">
-        <v>78321</v>
-      </c>
-      <c r="D96" t="s">
-        <v>303</v>
-      </c>
       <c r="E96" t="s">
+        <v>131</v>
+      </c>
+      <c r="F96" t="s">
         <v>327</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>328</v>
       </c>
-      <c r="G96" t="s">
-        <v>329</v>
-      </c>
-      <c r="H96"/>
+      <c r="H96" t="s">
+        <v>323</v>
+      </c>
       <c r="I96" t="s">
+        <v>324</v>
+      </c>
+      <c r="J96" t="s">
         <v>325</v>
       </c>
-      <c r="J96" t="s">
-        <v>320</v>
-      </c>
       <c r="K96" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L96" t="s">
         <v>326</v>
@@ -6665,35 +6676,37 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97">
-        <v>8</v>
+        <v>78321</v>
       </c>
       <c r="B97" t="s">
+        <v>301</v>
+      </c>
+      <c r="C97">
+        <v>8</v>
+      </c>
+      <c r="D97" t="s">
         <v>193</v>
       </c>
-      <c r="C97">
-        <v>78321</v>
-      </c>
-      <c r="D97" t="s">
-        <v>303</v>
-      </c>
       <c r="E97" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F97" t="s">
+        <v>327</v>
+      </c>
+      <c r="G97" t="s">
         <v>328</v>
       </c>
-      <c r="G97" t="s">
-        <v>329</v>
-      </c>
-      <c r="H97"/>
+      <c r="H97" t="s">
+        <v>323</v>
+      </c>
       <c r="I97" t="s">
+        <v>324</v>
+      </c>
+      <c r="J97" t="s">
         <v>325</v>
       </c>
-      <c r="J97" t="s">
-        <v>320</v>
-      </c>
       <c r="K97" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L97" t="s">
         <v>326</v>
@@ -6701,928 +6714,928 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98">
-        <v>8</v>
+        <v>78322</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>330</v>
       </c>
       <c r="C98">
-        <v>78322</v>
+        <v>8</v>
       </c>
       <c r="D98" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" t="s">
         <v>331</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>332</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>333</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>334</v>
       </c>
-      <c r="H98" t="s">
+      <c r="I98" t="s">
         <v>335</v>
       </c>
-      <c r="I98" t="s">
+      <c r="J98" t="s">
         <v>336</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>337</v>
       </c>
-      <c r="K98" t="s">
+      <c r="L98" t="s">
         <v>338</v>
-      </c>
-      <c r="L98" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99">
-        <v>8</v>
+        <v>78322</v>
       </c>
       <c r="B99" t="s">
+        <v>330</v>
+      </c>
+      <c r="C99">
+        <v>8</v>
+      </c>
+      <c r="D99" t="s">
         <v>22</v>
       </c>
-      <c r="C99">
-        <v>78322</v>
-      </c>
-      <c r="D99" t="s">
-        <v>331</v>
-      </c>
       <c r="E99" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F99" t="s">
+        <v>332</v>
+      </c>
+      <c r="G99" t="s">
         <v>333</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>334</v>
       </c>
-      <c r="H99" t="s">
+      <c r="I99" t="s">
         <v>335</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>336</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>337</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" t="s">
         <v>338</v>
-      </c>
-      <c r="L99" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100">
-        <v>8</v>
+        <v>78322</v>
       </c>
       <c r="B100" t="s">
+        <v>330</v>
+      </c>
+      <c r="C100">
+        <v>8</v>
+      </c>
+      <c r="D100" t="s">
         <v>23</v>
       </c>
-      <c r="C100">
-        <v>78322</v>
-      </c>
-      <c r="D100" t="s">
-        <v>331</v>
-      </c>
       <c r="E100" t="s">
+        <v>340</v>
+      </c>
+      <c r="F100" t="s">
         <v>341</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>342</v>
       </c>
-      <c r="G100" t="s">
-        <v>343</v>
-      </c>
       <c r="H100" t="s">
+        <v>334</v>
+      </c>
+      <c r="I100" t="s">
         <v>335</v>
       </c>
-      <c r="I100" t="s">
+      <c r="J100" t="s">
         <v>336</v>
       </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>337</v>
       </c>
-      <c r="K100" t="s">
+      <c r="L100" t="s">
         <v>338</v>
-      </c>
-      <c r="L100" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101">
-        <v>8</v>
+        <v>78322</v>
       </c>
       <c r="B101" t="s">
+        <v>330</v>
+      </c>
+      <c r="C101">
+        <v>8</v>
+      </c>
+      <c r="D101" t="s">
         <v>29</v>
       </c>
-      <c r="C101">
-        <v>78322</v>
-      </c>
-      <c r="D101" t="s">
-        <v>331</v>
-      </c>
       <c r="E101" t="s">
+        <v>340</v>
+      </c>
+      <c r="F101" t="s">
         <v>341</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>342</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>343</v>
       </c>
-      <c r="H101" t="s">
-        <v>344</v>
-      </c>
       <c r="I101" t="s">
+        <v>335</v>
+      </c>
+      <c r="J101" t="s">
         <v>336</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>337</v>
       </c>
-      <c r="K101" t="s">
+      <c r="L101" t="s">
         <v>338</v>
-      </c>
-      <c r="L101" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102">
-        <v>8</v>
+        <v>78322</v>
       </c>
       <c r="B102" t="s">
+        <v>330</v>
+      </c>
+      <c r="C102">
+        <v>8</v>
+      </c>
+      <c r="D102" t="s">
         <v>33</v>
       </c>
-      <c r="C102">
-        <v>78322</v>
-      </c>
-      <c r="D102" t="s">
-        <v>331</v>
-      </c>
       <c r="E102" t="s">
+        <v>344</v>
+      </c>
+      <c r="F102" t="s">
         <v>345</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>346</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
+        <v>343</v>
+      </c>
+      <c r="I102" t="s">
         <v>347</v>
       </c>
-      <c r="H102" t="s">
-        <v>344</v>
-      </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
+        <v>336</v>
+      </c>
+      <c r="K102" t="s">
+        <v>337</v>
+      </c>
+      <c r="L102" t="s">
         <v>348</v>
-      </c>
-      <c r="J102" t="s">
-        <v>337</v>
-      </c>
-      <c r="K102" t="s">
-        <v>338</v>
-      </c>
-      <c r="L102" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103">
-        <v>8</v>
+        <v>78322</v>
       </c>
       <c r="B103" t="s">
+        <v>330</v>
+      </c>
+      <c r="C103">
+        <v>8</v>
+      </c>
+      <c r="D103" t="s">
         <v>40</v>
       </c>
-      <c r="C103">
-        <v>78322</v>
-      </c>
-      <c r="D103" t="s">
-        <v>331</v>
-      </c>
       <c r="E103" t="s">
+        <v>344</v>
+      </c>
+      <c r="F103" t="s">
         <v>345</v>
       </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>346</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
+        <v>349</v>
+      </c>
+      <c r="I103" t="s">
         <v>347</v>
       </c>
-      <c r="H103" t="s">
+      <c r="J103" t="s">
         <v>350</v>
       </c>
-      <c r="I103" t="s">
+      <c r="K103" t="s">
+        <v>351</v>
+      </c>
+      <c r="L103" t="s">
         <v>348</v>
-      </c>
-      <c r="J103" t="s">
-        <v>351</v>
-      </c>
-      <c r="K103" t="s">
-        <v>352</v>
-      </c>
-      <c r="L103" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104">
-        <v>8</v>
+        <v>78322</v>
       </c>
       <c r="B104" t="s">
+        <v>330</v>
+      </c>
+      <c r="C104">
+        <v>8</v>
+      </c>
+      <c r="D104" t="s">
         <v>41</v>
       </c>
-      <c r="C104">
-        <v>78322</v>
-      </c>
-      <c r="D104" t="s">
-        <v>331</v>
-      </c>
       <c r="E104" t="s">
+        <v>352</v>
+      </c>
+      <c r="F104" t="s">
         <v>353</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>354</v>
       </c>
-      <c r="G104" t="s">
-        <v>355</v>
-      </c>
       <c r="H104" t="s">
+        <v>349</v>
+      </c>
+      <c r="I104" t="s">
+        <v>347</v>
+      </c>
+      <c r="J104" t="s">
         <v>350</v>
       </c>
-      <c r="I104" t="s">
+      <c r="K104" t="s">
+        <v>351</v>
+      </c>
+      <c r="L104" t="s">
         <v>348</v>
-      </c>
-      <c r="J104" t="s">
-        <v>351</v>
-      </c>
-      <c r="K104" t="s">
-        <v>352</v>
-      </c>
-      <c r="L104" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105">
-        <v>8</v>
+        <v>78322</v>
       </c>
       <c r="B105" t="s">
+        <v>330</v>
+      </c>
+      <c r="C105">
+        <v>8</v>
+      </c>
+      <c r="D105" t="s">
         <v>46</v>
       </c>
-      <c r="C105">
-        <v>78322</v>
-      </c>
-      <c r="D105" t="s">
-        <v>331</v>
-      </c>
       <c r="E105" t="s">
+        <v>352</v>
+      </c>
+      <c r="F105" t="s">
         <v>353</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>354</v>
       </c>
-      <c r="G105" t="s">
-        <v>355</v>
-      </c>
       <c r="H105" t="s">
+        <v>349</v>
+      </c>
+      <c r="I105" t="s">
+        <v>347</v>
+      </c>
+      <c r="J105" t="s">
         <v>350</v>
       </c>
-      <c r="I105" t="s">
+      <c r="K105" t="s">
+        <v>351</v>
+      </c>
+      <c r="L105" t="s">
         <v>348</v>
-      </c>
-      <c r="J105" t="s">
-        <v>351</v>
-      </c>
-      <c r="K105" t="s">
-        <v>352</v>
-      </c>
-      <c r="L105" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>355</v>
       </c>
       <c r="C106">
-        <v>78323</v>
+        <v>8</v>
       </c>
       <c r="D106" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
         <v>356</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>357</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>358</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>359</v>
       </c>
-      <c r="H106" t="s">
+      <c r="I106" t="s">
         <v>360</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>361</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>362</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" t="s">
         <v>363</v>
-      </c>
-      <c r="L106" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B107" t="s">
+        <v>355</v>
+      </c>
+      <c r="C107">
+        <v>8</v>
+      </c>
+      <c r="D107" t="s">
         <v>22</v>
       </c>
-      <c r="C107">
-        <v>78323</v>
-      </c>
-      <c r="D107" t="s">
-        <v>356</v>
-      </c>
       <c r="E107" t="s">
+        <v>364</v>
+      </c>
+      <c r="F107" t="s">
+        <v>357</v>
+      </c>
+      <c r="G107" t="s">
+        <v>358</v>
+      </c>
+      <c r="H107" t="s">
+        <v>359</v>
+      </c>
+      <c r="I107" t="s">
+        <v>360</v>
+      </c>
+      <c r="J107" t="s">
+        <v>361</v>
+      </c>
+      <c r="K107" t="s">
+        <v>362</v>
+      </c>
+      <c r="L107" t="s">
         <v>365</v>
-      </c>
-      <c r="F107" t="s">
-        <v>358</v>
-      </c>
-      <c r="G107" t="s">
-        <v>359</v>
-      </c>
-      <c r="H107" t="s">
-        <v>360</v>
-      </c>
-      <c r="I107" t="s">
-        <v>361</v>
-      </c>
-      <c r="J107" t="s">
-        <v>362</v>
-      </c>
-      <c r="K107" t="s">
-        <v>363</v>
-      </c>
-      <c r="L107" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B108" t="s">
+        <v>355</v>
+      </c>
+      <c r="C108">
+        <v>8</v>
+      </c>
+      <c r="D108" t="s">
         <v>23</v>
       </c>
-      <c r="C108">
-        <v>78323</v>
-      </c>
-      <c r="D108" t="s">
-        <v>356</v>
-      </c>
       <c r="E108" t="s">
+        <v>366</v>
+      </c>
+      <c r="F108" t="s">
         <v>367</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>368</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
+        <v>359</v>
+      </c>
+      <c r="I108" t="s">
+        <v>360</v>
+      </c>
+      <c r="J108" t="s">
+        <v>361</v>
+      </c>
+      <c r="K108" t="s">
+        <v>362</v>
+      </c>
+      <c r="L108" t="s">
         <v>369</v>
-      </c>
-      <c r="H108" t="s">
-        <v>360</v>
-      </c>
-      <c r="I108" t="s">
-        <v>361</v>
-      </c>
-      <c r="J108" t="s">
-        <v>362</v>
-      </c>
-      <c r="K108" t="s">
-        <v>363</v>
-      </c>
-      <c r="L108" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B109" t="s">
+        <v>355</v>
+      </c>
+      <c r="C109">
+        <v>8</v>
+      </c>
+      <c r="D109" t="s">
         <v>29</v>
       </c>
-      <c r="C109">
-        <v>78323</v>
-      </c>
-      <c r="D109" t="s">
-        <v>356</v>
-      </c>
       <c r="E109" t="s">
+        <v>366</v>
+      </c>
+      <c r="F109" t="s">
         <v>367</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>368</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
+        <v>359</v>
+      </c>
+      <c r="I109" t="s">
+        <v>360</v>
+      </c>
+      <c r="J109" t="s">
+        <v>361</v>
+      </c>
+      <c r="K109" t="s">
+        <v>362</v>
+      </c>
+      <c r="L109" t="s">
         <v>369</v>
-      </c>
-      <c r="H109" t="s">
-        <v>360</v>
-      </c>
-      <c r="I109" t="s">
-        <v>361</v>
-      </c>
-      <c r="J109" t="s">
-        <v>362</v>
-      </c>
-      <c r="K109" t="s">
-        <v>363</v>
-      </c>
-      <c r="L109" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B110" t="s">
+        <v>355</v>
+      </c>
+      <c r="C110">
+        <v>8</v>
+      </c>
+      <c r="D110" t="s">
         <v>33</v>
       </c>
-      <c r="C110">
-        <v>78323</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>356</v>
       </c>
-      <c r="E110" t="s">
-        <v>357</v>
-      </c>
       <c r="F110" t="s">
+        <v>370</v>
+      </c>
+      <c r="G110" t="s">
         <v>371</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" t="s">
         <v>372</v>
       </c>
-      <c r="H110" t="s">
+      <c r="I110" t="s">
         <v>373</v>
       </c>
-      <c r="I110" t="s">
+      <c r="J110" t="s">
         <v>374</v>
       </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
         <v>375</v>
       </c>
-      <c r="K110" t="s">
-        <v>376</v>
-      </c>
       <c r="L110" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B111" t="s">
+        <v>355</v>
+      </c>
+      <c r="C111">
+        <v>8</v>
+      </c>
+      <c r="D111" t="s">
         <v>40</v>
       </c>
-      <c r="C111">
-        <v>78323</v>
-      </c>
-      <c r="D111" t="s">
-        <v>356</v>
-      </c>
       <c r="E111" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F111" t="s">
+        <v>370</v>
+      </c>
+      <c r="G111" t="s">
         <v>371</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>372</v>
       </c>
-      <c r="H111" t="s">
+      <c r="I111" t="s">
         <v>373</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>374</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>375</v>
       </c>
-      <c r="K111" t="s">
-        <v>376</v>
-      </c>
       <c r="L111" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B112" t="s">
+        <v>355</v>
+      </c>
+      <c r="C112">
+        <v>8</v>
+      </c>
+      <c r="D112" t="s">
         <v>41</v>
       </c>
-      <c r="C112">
-        <v>78323</v>
-      </c>
-      <c r="D112" t="s">
-        <v>356</v>
-      </c>
       <c r="E112" t="s">
+        <v>377</v>
+      </c>
+      <c r="F112" t="s">
         <v>378</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>379</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>380</v>
       </c>
-      <c r="H112" t="s">
-        <v>381</v>
-      </c>
       <c r="I112" t="s">
+        <v>373</v>
+      </c>
+      <c r="J112" t="s">
         <v>374</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>375</v>
       </c>
-      <c r="K112" t="s">
-        <v>376</v>
-      </c>
       <c r="L112" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B113" t="s">
+        <v>355</v>
+      </c>
+      <c r="C113">
+        <v>8</v>
+      </c>
+      <c r="D113" t="s">
         <v>46</v>
       </c>
-      <c r="C113">
-        <v>78323</v>
-      </c>
-      <c r="D113" t="s">
-        <v>356</v>
-      </c>
       <c r="E113" t="s">
+        <v>377</v>
+      </c>
+      <c r="F113" t="s">
         <v>378</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>379</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>380</v>
       </c>
-      <c r="H113" t="s">
+      <c r="I113" t="s">
+        <v>373</v>
+      </c>
+      <c r="J113" t="s">
+        <v>374</v>
+      </c>
+      <c r="K113" t="s">
+        <v>375</v>
+      </c>
+      <c r="L113" t="s">
         <v>381</v>
-      </c>
-      <c r="I113" t="s">
-        <v>374</v>
-      </c>
-      <c r="J113" t="s">
-        <v>375</v>
-      </c>
-      <c r="K113" t="s">
-        <v>376</v>
-      </c>
-      <c r="L113" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B114" t="s">
+        <v>355</v>
+      </c>
+      <c r="C114">
+        <v>8</v>
+      </c>
+      <c r="D114" t="s">
         <v>189</v>
       </c>
-      <c r="C114">
-        <v>78323</v>
-      </c>
-      <c r="D114" t="s">
-        <v>356</v>
-      </c>
       <c r="E114" t="s">
+        <v>382</v>
+      </c>
+      <c r="F114" t="s">
         <v>383</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>384</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>385</v>
       </c>
-      <c r="H114" t="s">
+      <c r="I114" t="s">
         <v>386</v>
       </c>
-      <c r="I114" t="s">
+      <c r="J114" t="s">
         <v>387</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>388</v>
       </c>
-      <c r="K114" t="s">
-        <v>389</v>
-      </c>
       <c r="L114" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B115" t="s">
+        <v>355</v>
+      </c>
+      <c r="C115">
+        <v>8</v>
+      </c>
+      <c r="D115" t="s">
         <v>193</v>
       </c>
-      <c r="C115">
-        <v>78323</v>
-      </c>
-      <c r="D115" t="s">
-        <v>356</v>
-      </c>
       <c r="E115" t="s">
+        <v>382</v>
+      </c>
+      <c r="F115" t="s">
         <v>383</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>384</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>385</v>
       </c>
-      <c r="H115" t="s">
+      <c r="I115" t="s">
         <v>386</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>387</v>
       </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>388</v>
       </c>
-      <c r="K115" t="s">
-        <v>389</v>
-      </c>
       <c r="L115" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B116" t="s">
+        <v>355</v>
+      </c>
+      <c r="C116">
+        <v>8</v>
+      </c>
+      <c r="D116" t="s">
         <v>198</v>
       </c>
-      <c r="C116">
-        <v>78323</v>
-      </c>
-      <c r="D116" t="s">
-        <v>356</v>
-      </c>
       <c r="E116" t="s">
+        <v>389</v>
+      </c>
+      <c r="F116" t="s">
         <v>390</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>391</v>
       </c>
-      <c r="G116" t="s">
-        <v>392</v>
-      </c>
       <c r="H116" t="s">
+        <v>385</v>
+      </c>
+      <c r="I116" t="s">
         <v>386</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J116" t="s">
         <v>387</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>388</v>
       </c>
-      <c r="K116" t="s">
-        <v>389</v>
-      </c>
       <c r="L116" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117">
-        <v>8</v>
+        <v>78323</v>
       </c>
       <c r="B117" t="s">
+        <v>355</v>
+      </c>
+      <c r="C117">
+        <v>8</v>
+      </c>
+      <c r="D117" t="s">
         <v>200</v>
       </c>
-      <c r="C117">
-        <v>78323</v>
-      </c>
-      <c r="D117" t="s">
-        <v>356</v>
-      </c>
       <c r="E117" t="s">
+        <v>389</v>
+      </c>
+      <c r="F117" t="s">
         <v>390</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>391</v>
       </c>
-      <c r="G117" t="s">
-        <v>392</v>
-      </c>
       <c r="H117" t="s">
+        <v>385</v>
+      </c>
+      <c r="I117" t="s">
         <v>386</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>387</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>388</v>
       </c>
-      <c r="K117" t="s">
-        <v>389</v>
-      </c>
       <c r="L117" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118">
-        <v>8</v>
+        <v>78324</v>
       </c>
       <c r="B118" t="s">
-        <v>12</v>
+        <v>392</v>
       </c>
       <c r="C118">
-        <v>78324</v>
+        <v>8</v>
       </c>
       <c r="D118" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" t="s">
         <v>393</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>394</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>395</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>396</v>
       </c>
-      <c r="H118" t="s">
+      <c r="I118" t="s">
         <v>397</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>398</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>399</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" t="s">
         <v>400</v>
-      </c>
-      <c r="L118" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119">
-        <v>8</v>
+        <v>78324</v>
       </c>
       <c r="B119" t="s">
+        <v>392</v>
+      </c>
+      <c r="C119">
+        <v>8</v>
+      </c>
+      <c r="D119" t="s">
         <v>22</v>
       </c>
-      <c r="C119">
-        <v>78324</v>
-      </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>393</v>
       </c>
-      <c r="E119" t="s">
-        <v>394</v>
-      </c>
       <c r="F119" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G119" t="s">
+        <v>395</v>
+      </c>
+      <c r="H119" t="s">
         <v>396</v>
       </c>
-      <c r="H119" t="s">
+      <c r="I119" t="s">
         <v>397</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>398</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>399</v>
       </c>
-      <c r="K119" t="s">
+      <c r="L119" t="s">
         <v>400</v>
-      </c>
-      <c r="L119" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120">
-        <v>8</v>
+        <v>78324</v>
       </c>
       <c r="B120" t="s">
+        <v>392</v>
+      </c>
+      <c r="C120">
+        <v>8</v>
+      </c>
+      <c r="D120" t="s">
         <v>23</v>
       </c>
-      <c r="C120">
-        <v>78324</v>
-      </c>
-      <c r="D120" t="s">
-        <v>393</v>
-      </c>
       <c r="E120" t="s">
+        <v>402</v>
+      </c>
+      <c r="F120" t="s">
+        <v>401</v>
+      </c>
+      <c r="G120" t="s">
         <v>403</v>
       </c>
-      <c r="F120" t="s">
-        <v>402</v>
-      </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
+        <v>396</v>
+      </c>
+      <c r="I120" t="s">
+        <v>397</v>
+      </c>
+      <c r="J120" t="s">
+        <v>398</v>
+      </c>
+      <c r="K120" t="s">
         <v>404</v>
       </c>
-      <c r="H120" t="s">
-        <v>397</v>
-      </c>
-      <c r="I120" t="s">
-        <v>398</v>
-      </c>
-      <c r="J120" t="s">
-        <v>399</v>
-      </c>
-      <c r="K120" t="s">
+      <c r="L120" t="s">
         <v>400</v>
-      </c>
-      <c r="L120" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121">
-        <v>8</v>
+        <v>78324</v>
       </c>
       <c r="B121" t="s">
+        <v>392</v>
+      </c>
+      <c r="C121">
+        <v>8</v>
+      </c>
+      <c r="D121" t="s">
         <v>29</v>
       </c>
-      <c r="C121">
-        <v>78324</v>
-      </c>
-      <c r="D121" t="s">
-        <v>393</v>
-      </c>
       <c r="E121" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F121" t="s">
         <v>405</v>
       </c>
       <c r="G121" t="s">
+        <v>403</v>
+      </c>
+      <c r="H121" t="s">
+        <v>396</v>
+      </c>
+      <c r="I121" t="s">
+        <v>397</v>
+      </c>
+      <c r="J121" t="s">
+        <v>398</v>
+      </c>
+      <c r="K121" t="s">
         <v>404</v>
       </c>
-      <c r="H121" t="s">
-        <v>397</v>
-      </c>
-      <c r="I121" t="s">
-        <v>398</v>
-      </c>
-      <c r="J121" t="s">
-        <v>399</v>
-      </c>
-      <c r="K121" t="s">
+      <c r="L121" t="s">
         <v>400</v>
-      </c>
-      <c r="L121" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122">
-        <v>8</v>
+        <v>78325</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>406</v>
       </c>
       <c r="C122">
-        <v>78325</v>
+        <v>8</v>
       </c>
       <c r="D122" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="E122" t="s">
         <v>407</v>
@@ -7651,16 +7664,16 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123">
-        <v>8</v>
+        <v>78325</v>
       </c>
       <c r="B123" t="s">
+        <v>406</v>
+      </c>
+      <c r="C123">
+        <v>8</v>
+      </c>
+      <c r="D123" t="s">
         <v>22</v>
-      </c>
-      <c r="C123">
-        <v>78325</v>
-      </c>
-      <c r="D123" t="s">
-        <v>406</v>
       </c>
       <c r="E123" t="s">
         <v>407</v>
@@ -7689,16 +7702,16 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124">
-        <v>8</v>
+        <v>78325</v>
       </c>
       <c r="B124" t="s">
+        <v>406</v>
+      </c>
+      <c r="C124">
+        <v>8</v>
+      </c>
+      <c r="D124" t="s">
         <v>23</v>
-      </c>
-      <c r="C124">
-        <v>78325</v>
-      </c>
-      <c r="D124" t="s">
-        <v>406</v>
       </c>
       <c r="E124" t="s">
         <v>416</v>
@@ -7727,16 +7740,16 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125">
-        <v>8</v>
+        <v>78325</v>
       </c>
       <c r="B125" t="s">
+        <v>406</v>
+      </c>
+      <c r="C125">
+        <v>8</v>
+      </c>
+      <c r="D125" t="s">
         <v>29</v>
-      </c>
-      <c r="C125">
-        <v>78325</v>
-      </c>
-      <c r="D125" t="s">
-        <v>406</v>
       </c>
       <c r="E125" t="s">
         <v>416</v>
@@ -7765,16 +7778,16 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126">
-        <v>8</v>
+        <v>78325</v>
       </c>
       <c r="B126" t="s">
+        <v>406</v>
+      </c>
+      <c r="C126">
+        <v>8</v>
+      </c>
+      <c r="D126" t="s">
         <v>33</v>
-      </c>
-      <c r="C126">
-        <v>78325</v>
-      </c>
-      <c r="D126" t="s">
-        <v>406</v>
       </c>
       <c r="E126" t="s">
         <v>420</v>
@@ -7803,16 +7816,16 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127">
-        <v>8</v>
+        <v>78325</v>
       </c>
       <c r="B127" t="s">
+        <v>406</v>
+      </c>
+      <c r="C127">
+        <v>8</v>
+      </c>
+      <c r="D127" t="s">
         <v>40</v>
-      </c>
-      <c r="C127">
-        <v>78325</v>
-      </c>
-      <c r="D127" t="s">
-        <v>406</v>
       </c>
       <c r="E127" t="s">
         <v>420</v>
@@ -7841,16 +7854,16 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128">
-        <v>8</v>
+        <v>78326</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>425</v>
       </c>
       <c r="C128">
-        <v>78326</v>
+        <v>8</v>
       </c>
       <c r="D128" t="s">
-        <v>425</v>
+        <v>13</v>
       </c>
       <c r="E128" t="s">
         <v>426</v>
@@ -7879,16 +7892,16 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129">
-        <v>8</v>
+        <v>78326</v>
       </c>
       <c r="B129" t="s">
+        <v>425</v>
+      </c>
+      <c r="C129">
+        <v>8</v>
+      </c>
+      <c r="D129" t="s">
         <v>22</v>
-      </c>
-      <c r="C129">
-        <v>78326</v>
-      </c>
-      <c r="D129" t="s">
-        <v>425</v>
       </c>
       <c r="E129" t="s">
         <v>426</v>
@@ -7917,16 +7930,16 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130">
-        <v>8</v>
+        <v>78327</v>
       </c>
       <c r="B130" t="s">
-        <v>12</v>
+        <v>433</v>
       </c>
       <c r="C130">
-        <v>78327</v>
+        <v>8</v>
       </c>
       <c r="D130" t="s">
-        <v>433</v>
+        <v>13</v>
       </c>
       <c r="E130" t="s">
         <v>434</v>
@@ -7955,16 +7968,16 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131">
-        <v>8</v>
+        <v>78327</v>
       </c>
       <c r="B131" t="s">
+        <v>433</v>
+      </c>
+      <c r="C131">
+        <v>8</v>
+      </c>
+      <c r="D131" t="s">
         <v>22</v>
-      </c>
-      <c r="C131">
-        <v>78327</v>
-      </c>
-      <c r="D131" t="s">
-        <v>433</v>
       </c>
       <c r="E131" t="s">
         <v>434</v>
@@ -7993,25 +8006,25 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132">
-        <v>8</v>
+        <v>78327</v>
       </c>
       <c r="B132" t="s">
+        <v>433</v>
+      </c>
+      <c r="C132">
+        <v>8</v>
+      </c>
+      <c r="D132" t="s">
         <v>23</v>
       </c>
-      <c r="C132">
-        <v>78327</v>
-      </c>
-      <c r="D132" t="s">
-        <v>433</v>
-      </c>
       <c r="E132" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="F132" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="G132" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="H132" t="s">
         <v>437</v>
@@ -8031,16 +8044,16 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133">
-        <v>8</v>
+        <v>78327</v>
       </c>
       <c r="B133" t="s">
+        <v>433</v>
+      </c>
+      <c r="C133">
+        <v>8</v>
+      </c>
+      <c r="D133" t="s">
         <v>29</v>
-      </c>
-      <c r="C133">
-        <v>78327</v>
-      </c>
-      <c r="D133" t="s">
-        <v>433</v>
       </c>
       <c r="E133" t="s">
         <v>442</v>
@@ -8069,54 +8082,54 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134">
-        <v>8</v>
+        <v>78327</v>
       </c>
       <c r="B134" t="s">
+        <v>433</v>
+      </c>
+      <c r="C134">
+        <v>8</v>
+      </c>
+      <c r="D134" t="s">
         <v>33</v>
       </c>
-      <c r="C134">
-        <v>78327</v>
-      </c>
-      <c r="D134" t="s">
-        <v>433</v>
-      </c>
       <c r="E134" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F134" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G134" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H134" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I134" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="J134" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="K134" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="L134" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
     </row>
     <row r="135" spans="1:12">
       <c r="A135">
-        <v>8</v>
+        <v>78327</v>
       </c>
       <c r="B135" t="s">
+        <v>433</v>
+      </c>
+      <c r="C135">
+        <v>8</v>
+      </c>
+      <c r="D135" t="s">
         <v>40</v>
-      </c>
-      <c r="C135">
-        <v>78327</v>
-      </c>
-      <c r="D135" t="s">
-        <v>433</v>
       </c>
       <c r="E135" t="s">
         <v>446</v>
@@ -8128,7 +8141,7 @@
         <v>448</v>
       </c>
       <c r="H135" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="I135" t="s">
         <v>450</v>
@@ -8145,25 +8158,25 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136">
-        <v>8</v>
+        <v>78327</v>
       </c>
       <c r="B136" t="s">
+        <v>433</v>
+      </c>
+      <c r="C136">
+        <v>8</v>
+      </c>
+      <c r="D136" t="s">
         <v>41</v>
       </c>
-      <c r="C136">
-        <v>78327</v>
-      </c>
-      <c r="D136" t="s">
-        <v>433</v>
-      </c>
       <c r="E136" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F136" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="G136" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="H136" t="s">
         <v>454</v>
@@ -8172,10 +8185,10 @@
         <v>450</v>
       </c>
       <c r="J136" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="K136" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="L136" t="s">
         <v>453</v>
@@ -8183,16 +8196,16 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137">
-        <v>8</v>
+        <v>78327</v>
       </c>
       <c r="B137" t="s">
+        <v>433</v>
+      </c>
+      <c r="C137">
+        <v>8</v>
+      </c>
+      <c r="D137" t="s">
         <v>46</v>
-      </c>
-      <c r="C137">
-        <v>78327</v>
-      </c>
-      <c r="D137" t="s">
-        <v>433</v>
       </c>
       <c r="E137" t="s">
         <v>455</v>
@@ -8213,7 +8226,7 @@
         <v>458</v>
       </c>
       <c r="K137" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="L137" t="s">
         <v>453</v>
@@ -8221,16 +8234,16 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138">
-        <v>8</v>
+        <v>78329</v>
       </c>
       <c r="B138" t="s">
-        <v>12</v>
+        <v>460</v>
       </c>
       <c r="C138">
-        <v>78329</v>
+        <v>8</v>
       </c>
       <c r="D138" t="s">
-        <v>460</v>
+        <v>13</v>
       </c>
       <c r="E138" t="s">
         <v>461</v>
@@ -8259,16 +8272,16 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139">
-        <v>8</v>
+        <v>78329</v>
       </c>
       <c r="B139" t="s">
+        <v>460</v>
+      </c>
+      <c r="C139">
+        <v>8</v>
+      </c>
+      <c r="D139" t="s">
         <v>22</v>
-      </c>
-      <c r="C139">
-        <v>78329</v>
-      </c>
-      <c r="D139" t="s">
-        <v>460</v>
       </c>
       <c r="E139" t="s">
         <v>461</v>
@@ -8297,16 +8310,16 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140">
-        <v>8</v>
+        <v>78329</v>
       </c>
       <c r="B140" t="s">
+        <v>460</v>
+      </c>
+      <c r="C140">
+        <v>8</v>
+      </c>
+      <c r="D140" t="s">
         <v>23</v>
-      </c>
-      <c r="C140">
-        <v>78329</v>
-      </c>
-      <c r="D140" t="s">
-        <v>460</v>
       </c>
       <c r="E140" t="s">
         <v>469</v>
@@ -8335,16 +8348,16 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141">
-        <v>8</v>
+        <v>78329</v>
       </c>
       <c r="B141" t="s">
+        <v>460</v>
+      </c>
+      <c r="C141">
+        <v>8</v>
+      </c>
+      <c r="D141" t="s">
         <v>29</v>
-      </c>
-      <c r="C141">
-        <v>78329</v>
-      </c>
-      <c r="D141" t="s">
-        <v>460</v>
       </c>
       <c r="E141" t="s">
         <v>469</v>
@@ -8373,16 +8386,16 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142">
-        <v>8</v>
+        <v>78329</v>
       </c>
       <c r="B142" t="s">
+        <v>460</v>
+      </c>
+      <c r="C142">
+        <v>8</v>
+      </c>
+      <c r="D142" t="s">
         <v>33</v>
-      </c>
-      <c r="C142">
-        <v>78329</v>
-      </c>
-      <c r="D142" t="s">
-        <v>460</v>
       </c>
       <c r="E142" t="s">
         <v>475</v>
@@ -8411,16 +8424,16 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143">
-        <v>8</v>
+        <v>78329</v>
       </c>
       <c r="B143" t="s">
+        <v>460</v>
+      </c>
+      <c r="C143">
+        <v>8</v>
+      </c>
+      <c r="D143" t="s">
         <v>40</v>
-      </c>
-      <c r="C143">
-        <v>78329</v>
-      </c>
-      <c r="D143" t="s">
-        <v>460</v>
       </c>
       <c r="E143" t="s">
         <v>475</v>
@@ -8449,16 +8462,16 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144">
-        <v>8</v>
+        <v>78329</v>
       </c>
       <c r="B144" t="s">
+        <v>460</v>
+      </c>
+      <c r="C144">
+        <v>8</v>
+      </c>
+      <c r="D144" t="s">
         <v>41</v>
-      </c>
-      <c r="C144">
-        <v>78329</v>
-      </c>
-      <c r="D144" t="s">
-        <v>460</v>
       </c>
       <c r="E144" t="s">
         <v>484</v>
@@ -8487,16 +8500,16 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145">
-        <v>8</v>
+        <v>78329</v>
       </c>
       <c r="B145" t="s">
+        <v>460</v>
+      </c>
+      <c r="C145">
+        <v>8</v>
+      </c>
+      <c r="D145" t="s">
         <v>46</v>
-      </c>
-      <c r="C145">
-        <v>78329</v>
-      </c>
-      <c r="D145" t="s">
-        <v>460</v>
       </c>
       <c r="E145" t="s">
         <v>484</v>
@@ -8525,16 +8538,16 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146">
-        <v>8</v>
+        <v>78332</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>488</v>
       </c>
       <c r="C146">
-        <v>78332</v>
+        <v>8</v>
       </c>
       <c r="D146" t="s">
-        <v>488</v>
+        <v>13</v>
       </c>
       <c r="E146" t="s">
         <v>489</v>
@@ -8563,16 +8576,16 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147">
-        <v>8</v>
+        <v>78332</v>
       </c>
       <c r="B147" t="s">
+        <v>488</v>
+      </c>
+      <c r="C147">
+        <v>8</v>
+      </c>
+      <c r="D147" t="s">
         <v>22</v>
-      </c>
-      <c r="C147">
-        <v>78332</v>
-      </c>
-      <c r="D147" t="s">
-        <v>488</v>
       </c>
       <c r="E147" t="s">
         <v>489</v>
@@ -8584,7 +8597,7 @@
         <v>491</v>
       </c>
       <c r="H147" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="I147" t="s">
         <v>493</v>
@@ -8601,28 +8614,28 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148">
-        <v>8</v>
+        <v>78332</v>
       </c>
       <c r="B148" t="s">
+        <v>488</v>
+      </c>
+      <c r="C148">
+        <v>8</v>
+      </c>
+      <c r="D148" t="s">
         <v>23</v>
-      </c>
-      <c r="C148">
-        <v>78332</v>
-      </c>
-      <c r="D148" t="s">
-        <v>488</v>
       </c>
       <c r="E148" t="s">
         <v>494</v>
       </c>
       <c r="F148" t="s">
+        <v>497</v>
+      </c>
+      <c r="G148" t="s">
         <v>498</v>
       </c>
-      <c r="G148" t="s">
-        <v>499</v>
-      </c>
       <c r="H148" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="I148" t="s">
         <v>493</v>
@@ -8639,607 +8652,607 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149">
-        <v>8</v>
+        <v>78333</v>
       </c>
       <c r="B149" t="s">
-        <v>12</v>
+        <v>499</v>
       </c>
       <c r="C149">
-        <v>78333</v>
+        <v>8</v>
       </c>
       <c r="D149" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" t="s">
         <v>500</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
         <v>501</v>
       </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
         <v>502</v>
       </c>
-      <c r="G149" t="s">
+      <c r="H149" t="s">
         <v>503</v>
       </c>
-      <c r="H149" t="s">
+      <c r="I149" t="s">
         <v>504</v>
       </c>
-      <c r="I149" t="s">
+      <c r="J149" t="s">
         <v>505</v>
       </c>
-      <c r="J149" t="s">
+      <c r="K149" t="s">
         <v>506</v>
       </c>
-      <c r="K149" t="s">
+      <c r="L149" t="s">
         <v>507</v>
-      </c>
-      <c r="L149" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="150" spans="1:12">
       <c r="A150">
-        <v>8</v>
+        <v>78333</v>
       </c>
       <c r="B150" t="s">
+        <v>499</v>
+      </c>
+      <c r="C150">
+        <v>8</v>
+      </c>
+      <c r="D150" t="s">
         <v>22</v>
       </c>
-      <c r="C150">
-        <v>78333</v>
-      </c>
-      <c r="D150" t="s">
+      <c r="E150" t="s">
         <v>500</v>
       </c>
-      <c r="E150" t="s">
+      <c r="F150" t="s">
         <v>501</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>502</v>
       </c>
-      <c r="G150" t="s">
+      <c r="H150" t="s">
         <v>503</v>
       </c>
-      <c r="H150" t="s">
-        <v>504</v>
-      </c>
       <c r="I150" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J150" t="s">
+        <v>505</v>
+      </c>
+      <c r="K150" t="s">
         <v>506</v>
       </c>
-      <c r="K150" t="s">
+      <c r="L150" t="s">
         <v>507</v>
-      </c>
-      <c r="L150" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="151" spans="1:12">
       <c r="A151">
-        <v>8</v>
+        <v>78333</v>
       </c>
       <c r="B151" t="s">
+        <v>499</v>
+      </c>
+      <c r="C151">
+        <v>8</v>
+      </c>
+      <c r="D151" t="s">
         <v>23</v>
       </c>
-      <c r="C151">
-        <v>78333</v>
-      </c>
-      <c r="D151" t="s">
-        <v>500</v>
-      </c>
       <c r="E151" t="s">
+        <v>509</v>
+      </c>
+      <c r="F151" t="s">
         <v>510</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
         <v>511</v>
       </c>
-      <c r="G151" t="s">
+      <c r="H151" t="s">
+        <v>507</v>
+      </c>
+      <c r="I151" t="s">
+        <v>504</v>
+      </c>
+      <c r="J151" t="s">
+        <v>505</v>
+      </c>
+      <c r="K151" t="s">
         <v>512</v>
       </c>
-      <c r="H151" t="s">
-        <v>508</v>
-      </c>
-      <c r="I151" t="s">
-        <v>505</v>
-      </c>
-      <c r="J151" t="s">
-        <v>506</v>
-      </c>
-      <c r="K151" t="s">
+      <c r="L151" t="s">
         <v>513</v>
-      </c>
-      <c r="L151" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="152" spans="1:12">
       <c r="A152">
-        <v>8</v>
+        <v>78333</v>
       </c>
       <c r="B152" t="s">
+        <v>499</v>
+      </c>
+      <c r="C152">
+        <v>8</v>
+      </c>
+      <c r="D152" t="s">
         <v>29</v>
       </c>
-      <c r="C152">
-        <v>78333</v>
-      </c>
-      <c r="D152" t="s">
-        <v>500</v>
-      </c>
       <c r="E152" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F152" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G152" t="s">
+        <v>511</v>
+      </c>
+      <c r="H152" t="s">
+        <v>507</v>
+      </c>
+      <c r="I152" t="s">
+        <v>504</v>
+      </c>
+      <c r="J152" t="s">
+        <v>505</v>
+      </c>
+      <c r="K152" t="s">
         <v>512</v>
       </c>
-      <c r="H152" t="s">
-        <v>508</v>
-      </c>
-      <c r="I152" t="s">
-        <v>505</v>
-      </c>
-      <c r="J152" t="s">
-        <v>506</v>
-      </c>
-      <c r="K152" t="s">
+      <c r="L152" t="s">
         <v>513</v>
-      </c>
-      <c r="L152" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="153" spans="1:12">
       <c r="A153">
-        <v>8</v>
+        <v>78335</v>
       </c>
       <c r="B153" t="s">
-        <v>12</v>
+        <v>515</v>
       </c>
       <c r="C153">
-        <v>78335</v>
+        <v>8</v>
       </c>
       <c r="D153" t="s">
+        <v>13</v>
+      </c>
+      <c r="E153" t="s">
         <v>516</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
         <v>517</v>
       </c>
-      <c r="F153" t="s">
+      <c r="G153" t="s">
         <v>518</v>
       </c>
-      <c r="G153" t="s">
+      <c r="H153" t="s">
         <v>519</v>
       </c>
-      <c r="H153" t="s">
+      <c r="I153" t="s">
         <v>520</v>
       </c>
-      <c r="I153" t="s">
+      <c r="J153" t="s">
         <v>521</v>
       </c>
-      <c r="J153" t="s">
+      <c r="K153" t="s">
         <v>522</v>
       </c>
-      <c r="K153" t="s">
+      <c r="L153" t="s">
         <v>523</v>
-      </c>
-      <c r="L153" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="154" spans="1:12">
       <c r="A154">
-        <v>8</v>
+        <v>78335</v>
       </c>
       <c r="B154" t="s">
+        <v>515</v>
+      </c>
+      <c r="C154">
+        <v>8</v>
+      </c>
+      <c r="D154" t="s">
         <v>22</v>
       </c>
-      <c r="C154">
-        <v>78335</v>
-      </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
         <v>516</v>
       </c>
-      <c r="E154" t="s">
-        <v>517</v>
-      </c>
       <c r="F154" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G154" t="s">
+        <v>518</v>
+      </c>
+      <c r="H154" t="s">
         <v>519</v>
       </c>
-      <c r="H154" t="s">
+      <c r="I154" t="s">
         <v>520</v>
       </c>
-      <c r="I154" t="s">
+      <c r="J154" t="s">
         <v>521</v>
       </c>
-      <c r="J154" t="s">
+      <c r="K154" t="s">
         <v>522</v>
       </c>
-      <c r="K154" t="s">
+      <c r="L154" t="s">
         <v>523</v>
-      </c>
-      <c r="L154" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="155" spans="1:12">
       <c r="A155">
-        <v>8</v>
+        <v>78335</v>
       </c>
       <c r="B155" t="s">
+        <v>515</v>
+      </c>
+      <c r="C155">
+        <v>8</v>
+      </c>
+      <c r="D155" t="s">
         <v>23</v>
       </c>
-      <c r="C155">
-        <v>78335</v>
-      </c>
-      <c r="D155" t="s">
-        <v>516</v>
-      </c>
       <c r="E155" t="s">
+        <v>525</v>
+      </c>
+      <c r="F155" t="s">
         <v>526</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>527</v>
       </c>
-      <c r="G155" t="s">
+      <c r="H155" t="s">
+        <v>519</v>
+      </c>
+      <c r="I155" t="s">
+        <v>520</v>
+      </c>
+      <c r="J155" t="s">
         <v>528</v>
       </c>
-      <c r="H155" t="s">
-        <v>520</v>
-      </c>
-      <c r="I155" t="s">
-        <v>521</v>
-      </c>
-      <c r="J155" t="s">
-        <v>529</v>
-      </c>
       <c r="K155" t="s">
+        <v>522</v>
+      </c>
+      <c r="L155" t="s">
         <v>523</v>
-      </c>
-      <c r="L155" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="156" spans="1:12">
       <c r="A156">
-        <v>8</v>
+        <v>78335</v>
       </c>
       <c r="B156" t="s">
+        <v>515</v>
+      </c>
+      <c r="C156">
+        <v>8</v>
+      </c>
+      <c r="D156" t="s">
         <v>29</v>
       </c>
-      <c r="C156">
-        <v>78335</v>
-      </c>
-      <c r="D156" t="s">
-        <v>516</v>
-      </c>
       <c r="E156" t="s">
+        <v>525</v>
+      </c>
+      <c r="F156" t="s">
         <v>526</v>
       </c>
-      <c r="F156" t="s">
-        <v>527</v>
-      </c>
       <c r="G156" t="s">
+        <v>529</v>
+      </c>
+      <c r="H156" t="s">
         <v>530</v>
       </c>
-      <c r="H156" t="s">
-        <v>531</v>
-      </c>
       <c r="I156" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J156" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K156" t="s">
+        <v>522</v>
+      </c>
+      <c r="L156" t="s">
         <v>523</v>
-      </c>
-      <c r="L156" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="157" spans="1:12">
       <c r="A157">
-        <v>8</v>
+        <v>78335</v>
       </c>
       <c r="B157" t="s">
+        <v>515</v>
+      </c>
+      <c r="C157">
+        <v>8</v>
+      </c>
+      <c r="D157" t="s">
         <v>33</v>
       </c>
-      <c r="C157">
-        <v>78335</v>
-      </c>
-      <c r="D157" t="s">
-        <v>516</v>
-      </c>
       <c r="E157" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F157" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G157" t="s">
+        <v>527</v>
+      </c>
+      <c r="H157" t="s">
+        <v>530</v>
+      </c>
+      <c r="I157" t="s">
+        <v>520</v>
+      </c>
+      <c r="J157" t="s">
         <v>528</v>
       </c>
-      <c r="H157" t="s">
-        <v>531</v>
-      </c>
-      <c r="I157" t="s">
-        <v>521</v>
-      </c>
-      <c r="J157" t="s">
-        <v>529</v>
-      </c>
       <c r="K157" t="s">
+        <v>522</v>
+      </c>
+      <c r="L157" t="s">
         <v>523</v>
-      </c>
-      <c r="L157" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="158" spans="1:12">
       <c r="A158">
-        <v>8</v>
+        <v>78337</v>
       </c>
       <c r="B158" t="s">
-        <v>12</v>
+        <v>532</v>
       </c>
       <c r="C158">
-        <v>78337</v>
+        <v>8</v>
       </c>
       <c r="D158" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" t="s">
         <v>533</v>
       </c>
-      <c r="E158" t="s">
+      <c r="F158" t="s">
         <v>534</v>
       </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
         <v>535</v>
       </c>
-      <c r="G158" t="s">
+      <c r="H158" t="s">
         <v>536</v>
       </c>
-      <c r="H158" t="s">
+      <c r="I158" t="s">
         <v>537</v>
       </c>
-      <c r="I158" t="s">
+      <c r="J158" t="s">
         <v>538</v>
       </c>
-      <c r="J158" t="s">
+      <c r="K158" t="s">
         <v>539</v>
       </c>
-      <c r="K158" t="s">
+      <c r="L158" t="s">
         <v>540</v>
-      </c>
-      <c r="L158" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159">
-        <v>8</v>
+        <v>78337</v>
       </c>
       <c r="B159" t="s">
+        <v>532</v>
+      </c>
+      <c r="C159">
+        <v>8</v>
+      </c>
+      <c r="D159" t="s">
         <v>22</v>
       </c>
-      <c r="C159">
-        <v>78337</v>
-      </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
         <v>533</v>
       </c>
-      <c r="E159" t="s">
-        <v>534</v>
-      </c>
       <c r="F159" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G159" t="s">
+        <v>535</v>
+      </c>
+      <c r="H159" t="s">
         <v>536</v>
       </c>
-      <c r="H159" t="s">
-        <v>543</v>
-      </c>
       <c r="I159" t="s">
+        <v>537</v>
+      </c>
+      <c r="J159" t="s">
         <v>538</v>
       </c>
-      <c r="J159" t="s">
+      <c r="K159" t="s">
         <v>539</v>
       </c>
-      <c r="K159" t="s">
+      <c r="L159" t="s">
         <v>540</v>
-      </c>
-      <c r="L159" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="160" spans="1:12">
       <c r="A160">
-        <v>8</v>
+        <v>78337</v>
       </c>
       <c r="B160" t="s">
+        <v>532</v>
+      </c>
+      <c r="C160">
+        <v>8</v>
+      </c>
+      <c r="D160" t="s">
         <v>23</v>
       </c>
-      <c r="C160">
-        <v>78337</v>
-      </c>
-      <c r="D160" t="s">
-        <v>533</v>
-      </c>
       <c r="E160" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F160" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G160" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H160" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="I160" t="s">
+        <v>537</v>
+      </c>
+      <c r="J160" t="s">
         <v>538</v>
       </c>
-      <c r="J160" t="s">
+      <c r="K160" t="s">
         <v>539</v>
       </c>
-      <c r="K160" t="s">
+      <c r="L160" t="s">
         <v>540</v>
-      </c>
-      <c r="L160" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="161" spans="1:12">
       <c r="A161">
-        <v>8</v>
+        <v>78341</v>
       </c>
       <c r="B161" t="s">
-        <v>12</v>
+        <v>544</v>
       </c>
       <c r="C161">
-        <v>78341</v>
+        <v>8</v>
       </c>
       <c r="D161" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" t="s">
+        <v>545</v>
+      </c>
+      <c r="F161" t="s">
         <v>546</v>
       </c>
-      <c r="E161" t="s">
+      <c r="G161" t="s">
         <v>547</v>
       </c>
-      <c r="F161" t="s">
+      <c r="H161" t="s">
         <v>548</v>
       </c>
-      <c r="G161" t="s">
+      <c r="I161" t="s">
         <v>549</v>
       </c>
-      <c r="H161" t="s">
+      <c r="J161" t="s">
         <v>550</v>
       </c>
-      <c r="I161" t="s">
+      <c r="K161" t="s">
         <v>551</v>
       </c>
-      <c r="J161" t="s">
+      <c r="L161" t="s">
         <v>552</v>
-      </c>
-      <c r="K161" t="s">
-        <v>553</v>
-      </c>
-      <c r="L161" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="162" spans="1:12">
       <c r="A162">
-        <v>8</v>
+        <v>78341</v>
       </c>
       <c r="B162" t="s">
+        <v>544</v>
+      </c>
+      <c r="C162">
+        <v>8</v>
+      </c>
+      <c r="D162" t="s">
         <v>22</v>
       </c>
-      <c r="C162">
-        <v>78341</v>
-      </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
+        <v>545</v>
+      </c>
+      <c r="F162" t="s">
         <v>546</v>
       </c>
-      <c r="E162" t="s">
+      <c r="G162" t="s">
         <v>547</v>
       </c>
-      <c r="F162" t="s">
-        <v>548</v>
-      </c>
-      <c r="G162" t="s">
+      <c r="H162" t="s">
+        <v>553</v>
+      </c>
+      <c r="I162" t="s">
         <v>549</v>
       </c>
-      <c r="H162" t="s">
-        <v>555</v>
-      </c>
-      <c r="I162" t="s">
+      <c r="J162" t="s">
+        <v>550</v>
+      </c>
+      <c r="K162" t="s">
         <v>551</v>
       </c>
-      <c r="J162" t="s">
+      <c r="L162" t="s">
         <v>552</v>
-      </c>
-      <c r="K162" t="s">
-        <v>553</v>
-      </c>
-      <c r="L162" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="163" spans="1:12">
       <c r="A163">
-        <v>8</v>
+        <v>78346</v>
       </c>
       <c r="B163" t="s">
-        <v>12</v>
+        <v>554</v>
       </c>
       <c r="C163">
-        <v>78346</v>
+        <v>8</v>
       </c>
       <c r="D163" t="s">
+        <v>13</v>
+      </c>
+      <c r="E163" t="s">
+        <v>555</v>
+      </c>
+      <c r="F163" t="s">
         <v>556</v>
       </c>
-      <c r="E163" t="s">
+      <c r="G163" t="s">
         <v>557</v>
       </c>
-      <c r="F163" t="s">
+      <c r="H163" t="s">
         <v>558</v>
       </c>
-      <c r="G163" t="s">
+      <c r="I163" t="s">
         <v>559</v>
       </c>
-      <c r="H163" t="s">
+      <c r="J163" t="s">
         <v>560</v>
       </c>
-      <c r="I163" t="s">
+      <c r="K163" t="s">
         <v>561</v>
       </c>
-      <c r="J163" t="s">
-        <v>562</v>
-      </c>
-      <c r="K163" t="s">
-        <v>563</v>
-      </c>
       <c r="L163" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="164" spans="1:12">
       <c r="A164">
-        <v>8</v>
+        <v>78346</v>
       </c>
       <c r="B164" t="s">
+        <v>554</v>
+      </c>
+      <c r="C164">
+        <v>8</v>
+      </c>
+      <c r="D164" t="s">
         <v>22</v>
       </c>
-      <c r="C164">
-        <v>78346</v>
-      </c>
-      <c r="D164" t="s">
-        <v>556</v>
-      </c>
       <c r="E164" t="s">
+        <v>562</v>
+      </c>
+      <c r="F164" t="s">
+        <v>563</v>
+      </c>
+      <c r="G164" t="s">
         <v>557</v>
       </c>
-      <c r="F164" t="s">
+      <c r="H164" t="s">
         <v>558</v>
       </c>
-      <c r="G164" t="s">
+      <c r="I164" t="s">
         <v>559</v>
       </c>
-      <c r="H164" t="s">
+      <c r="J164" t="s">
         <v>560</v>
       </c>
-      <c r="I164" t="s">
+      <c r="K164" t="s">
         <v>561</v>
-      </c>
-      <c r="J164" t="s">
-        <v>562</v>
-      </c>
-      <c r="K164" t="s">
-        <v>563</v>
       </c>
       <c r="L164" t="s">
         <v>564</v>
@@ -9247,37 +9260,37 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165">
-        <v>8</v>
+        <v>78346</v>
       </c>
       <c r="B165" t="s">
+        <v>554</v>
+      </c>
+      <c r="C165">
+        <v>8</v>
+      </c>
+      <c r="D165" t="s">
         <v>23</v>
       </c>
-      <c r="C165">
-        <v>78346</v>
-      </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
+        <v>562</v>
+      </c>
+      <c r="F165" t="s">
         <v>556</v>
       </c>
-      <c r="E165" t="s">
+      <c r="G165" t="s">
         <v>565</v>
       </c>
-      <c r="F165" t="s">
-        <v>558</v>
-      </c>
-      <c r="G165" t="s">
+      <c r="H165" t="s">
         <v>566</v>
       </c>
-      <c r="H165" t="s">
+      <c r="I165" t="s">
+        <v>559</v>
+      </c>
+      <c r="J165" t="s">
         <v>560</v>
       </c>
-      <c r="I165" t="s">
+      <c r="K165" t="s">
         <v>561</v>
-      </c>
-      <c r="J165" t="s">
-        <v>562</v>
-      </c>
-      <c r="K165" t="s">
-        <v>563</v>
       </c>
       <c r="L165" t="s">
         <v>564</v>
@@ -9285,16 +9298,16 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166">
-        <v>8</v>
+        <v>78347</v>
       </c>
       <c r="B166" t="s">
-        <v>12</v>
+        <v>567</v>
       </c>
       <c r="C166">
-        <v>78347</v>
+        <v>8</v>
       </c>
       <c r="D166" t="s">
-        <v>567</v>
+        <v>13</v>
       </c>
       <c r="E166" t="s">
         <v>568</v>
@@ -9323,16 +9336,16 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167">
-        <v>8</v>
+        <v>78347</v>
       </c>
       <c r="B167" t="s">
+        <v>567</v>
+      </c>
+      <c r="C167">
+        <v>8</v>
+      </c>
+      <c r="D167" t="s">
         <v>22</v>
-      </c>
-      <c r="C167">
-        <v>78347</v>
-      </c>
-      <c r="D167" t="s">
-        <v>567</v>
       </c>
       <c r="E167" t="s">
         <v>568</v>
@@ -9361,16 +9374,16 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168">
-        <v>8</v>
+        <v>78348</v>
       </c>
       <c r="B168" t="s">
-        <v>12</v>
+        <v>576</v>
       </c>
       <c r="C168">
-        <v>78348</v>
+        <v>8</v>
       </c>
       <c r="D168" t="s">
-        <v>576</v>
+        <v>13</v>
       </c>
       <c r="E168" t="s">
         <v>577</v>
@@ -9399,25 +9412,25 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169">
-        <v>8</v>
+        <v>78348</v>
       </c>
       <c r="B169" t="s">
+        <v>576</v>
+      </c>
+      <c r="C169">
+        <v>8</v>
+      </c>
+      <c r="D169" t="s">
         <v>22</v>
       </c>
-      <c r="C169">
-        <v>78348</v>
-      </c>
-      <c r="D169" t="s">
-        <v>576</v>
-      </c>
       <c r="E169" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="F169" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G169" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H169" t="s">
         <v>580</v>
@@ -9437,19 +9450,19 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170">
-        <v>8</v>
+        <v>78348</v>
       </c>
       <c r="B170" t="s">
+        <v>576</v>
+      </c>
+      <c r="C170">
+        <v>8</v>
+      </c>
+      <c r="D170" t="s">
         <v>23</v>
       </c>
-      <c r="C170">
-        <v>78348</v>
-      </c>
-      <c r="D170" t="s">
-        <v>576</v>
-      </c>
       <c r="E170" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="F170" t="s">
         <v>578</v>
@@ -9475,312 +9488,309 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171">
-        <v>8</v>
+        <v>78349</v>
       </c>
       <c r="B171" t="s">
-        <v>12</v>
+        <v>588</v>
       </c>
       <c r="C171">
-        <v>78349</v>
+        <v>8</v>
       </c>
       <c r="D171" t="s">
-        <v>587</v>
+        <v>13</v>
       </c>
       <c r="E171" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F171" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G171" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H171" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I171" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J171" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K171" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L171" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="172" spans="1:12">
       <c r="A172">
-        <v>8</v>
+        <v>78349</v>
       </c>
       <c r="B172" t="s">
+        <v>588</v>
+      </c>
+      <c r="C172">
+        <v>8</v>
+      </c>
+      <c r="D172" t="s">
         <v>22</v>
       </c>
-      <c r="C172">
-        <v>78349</v>
-      </c>
-      <c r="D172" t="s">
-        <v>587</v>
-      </c>
       <c r="E172" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F172" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G172" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H172" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I172" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J172" t="s">
+        <v>597</v>
+      </c>
+      <c r="K172" t="s">
+        <v>595</v>
+      </c>
+      <c r="L172" t="s">
         <v>596</v>
-      </c>
-      <c r="K172" t="s">
-        <v>594</v>
-      </c>
-      <c r="L172" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="173" spans="1:12">
       <c r="A173">
-        <v>8</v>
+        <v>78349</v>
       </c>
       <c r="B173" t="s">
+        <v>588</v>
+      </c>
+      <c r="C173">
+        <v>8</v>
+      </c>
+      <c r="D173" t="s">
         <v>23</v>
       </c>
-      <c r="C173">
-        <v>78349</v>
-      </c>
-      <c r="D173" t="s">
-        <v>587</v>
-      </c>
       <c r="E173" t="s">
+        <v>598</v>
+      </c>
+      <c r="F173" t="s">
+        <v>599</v>
+      </c>
+      <c r="G173" t="s">
+        <v>600</v>
+      </c>
+      <c r="H173" t="s">
+        <v>592</v>
+      </c>
+      <c r="I173" t="s">
+        <v>601</v>
+      </c>
+      <c r="J173" t="s">
         <v>597</v>
       </c>
-      <c r="F173" t="s">
-        <v>598</v>
-      </c>
-      <c r="G173" t="s">
-        <v>599</v>
-      </c>
-      <c r="H173" t="s">
-        <v>591</v>
-      </c>
-      <c r="I173" t="s">
-        <v>600</v>
-      </c>
-      <c r="J173" t="s">
-        <v>596</v>
-      </c>
       <c r="K173" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L173" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="174" spans="1:12">
       <c r="A174">
-        <v>8</v>
+        <v>78349</v>
       </c>
       <c r="B174" t="s">
+        <v>588</v>
+      </c>
+      <c r="C174">
+        <v>8</v>
+      </c>
+      <c r="D174" t="s">
         <v>29</v>
       </c>
-      <c r="C174">
-        <v>78349</v>
-      </c>
-      <c r="D174" t="s">
-        <v>587</v>
-      </c>
       <c r="E174" t="s">
+        <v>598</v>
+      </c>
+      <c r="F174" t="s">
+        <v>599</v>
+      </c>
+      <c r="G174" t="s">
+        <v>600</v>
+      </c>
+      <c r="H174" t="s">
+        <v>592</v>
+      </c>
+      <c r="I174" t="s">
+        <v>593</v>
+      </c>
+      <c r="J174" t="s">
         <v>597</v>
       </c>
-      <c r="F174" t="s">
-        <v>598</v>
-      </c>
-      <c r="G174" t="s">
-        <v>599</v>
-      </c>
-      <c r="H174" t="s">
-        <v>591</v>
-      </c>
-      <c r="I174" t="s">
-        <v>592</v>
-      </c>
-      <c r="J174" t="s">
-        <v>596</v>
-      </c>
       <c r="K174" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L174" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="175" spans="1:12">
       <c r="A175">
-        <v>8</v>
+        <v>78349</v>
       </c>
       <c r="B175" t="s">
+        <v>588</v>
+      </c>
+      <c r="C175">
+        <v>8</v>
+      </c>
+      <c r="D175" t="s">
         <v>33</v>
       </c>
-      <c r="C175">
-        <v>78349</v>
-      </c>
-      <c r="D175" t="s">
-        <v>587</v>
-      </c>
       <c r="E175" t="s">
+        <v>603</v>
+      </c>
+      <c r="F175" t="s">
+        <v>604</v>
+      </c>
+      <c r="G175" t="s">
+        <v>605</v>
+      </c>
+      <c r="H175" t="s">
+        <v>606</v>
+      </c>
+      <c r="I175" t="s">
+        <v>593</v>
+      </c>
+      <c r="J175" t="s">
+        <v>597</v>
+      </c>
+      <c r="K175" t="s">
+        <v>595</v>
+      </c>
+      <c r="L175" t="s">
         <v>602</v>
-      </c>
-      <c r="F175" t="s">
-        <v>603</v>
-      </c>
-      <c r="G175" t="s">
-        <v>604</v>
-      </c>
-      <c r="H175" t="s">
-        <v>605</v>
-      </c>
-      <c r="I175" t="s">
-        <v>592</v>
-      </c>
-      <c r="J175" t="s">
-        <v>596</v>
-      </c>
-      <c r="K175" t="s">
-        <v>594</v>
-      </c>
-      <c r="L175" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="176" spans="1:12">
       <c r="A176">
-        <v>8</v>
+        <v>78349</v>
       </c>
       <c r="B176" t="s">
+        <v>588</v>
+      </c>
+      <c r="C176">
+        <v>8</v>
+      </c>
+      <c r="D176" t="s">
         <v>40</v>
       </c>
-      <c r="C176">
-        <v>78349</v>
-      </c>
-      <c r="D176" t="s">
-        <v>587</v>
-      </c>
       <c r="E176" t="s">
+        <v>603</v>
+      </c>
+      <c r="F176" t="s">
+        <v>604</v>
+      </c>
+      <c r="G176" t="s">
+        <v>605</v>
+      </c>
+      <c r="H176" t="s">
+        <v>606</v>
+      </c>
+      <c r="I176" t="s">
+        <v>593</v>
+      </c>
+      <c r="J176" t="s">
+        <v>597</v>
+      </c>
+      <c r="K176" t="s">
+        <v>595</v>
+      </c>
+      <c r="L176" t="s">
         <v>602</v>
-      </c>
-      <c r="F176" t="s">
-        <v>603</v>
-      </c>
-      <c r="G176" t="s">
-        <v>604</v>
-      </c>
-      <c r="H176" t="s">
-        <v>605</v>
-      </c>
-      <c r="I176" t="s">
-        <v>592</v>
-      </c>
-      <c r="J176" t="s">
-        <v>596</v>
-      </c>
-      <c r="K176" t="s">
-        <v>594</v>
-      </c>
-      <c r="L176" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="177" spans="1:12">
       <c r="A177">
-        <v>8</v>
+        <v>78349</v>
       </c>
       <c r="B177" t="s">
+        <v>588</v>
+      </c>
+      <c r="C177">
+        <v>8</v>
+      </c>
+      <c r="D177" t="s">
         <v>41</v>
       </c>
-      <c r="C177">
-        <v>78349</v>
-      </c>
-      <c r="D177" t="s">
-        <v>587</v>
-      </c>
       <c r="E177" t="s">
+        <v>607</v>
+      </c>
+      <c r="F177" t="s">
+        <v>608</v>
+      </c>
+      <c r="G177" t="s">
+        <v>609</v>
+      </c>
+      <c r="H177" t="s">
         <v>606</v>
       </c>
-      <c r="F177" t="s">
-        <v>607</v>
-      </c>
-      <c r="G177" t="s">
-        <v>608</v>
-      </c>
-      <c r="H177" t="s">
-        <v>605</v>
-      </c>
       <c r="I177" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J177" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K177" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L177" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="178" spans="1:12">
       <c r="A178">
-        <v>8</v>
+        <v>78349</v>
       </c>
       <c r="B178" t="s">
+        <v>588</v>
+      </c>
+      <c r="C178">
+        <v>8</v>
+      </c>
+      <c r="D178" t="s">
         <v>46</v>
       </c>
-      <c r="C178">
-        <v>78349</v>
-      </c>
-      <c r="D178" t="s">
-        <v>587</v>
-      </c>
       <c r="E178" t="s">
+        <v>607</v>
+      </c>
+      <c r="F178" t="s">
+        <v>611</v>
+      </c>
+      <c r="G178" t="s">
+        <v>609</v>
+      </c>
+      <c r="H178" t="s">
         <v>606</v>
       </c>
-      <c r="F178" t="s">
-        <v>607</v>
-      </c>
-      <c r="G178" t="s">
-        <v>608</v>
-      </c>
-      <c r="H178" t="s">
-        <v>605</v>
-      </c>
       <c r="I178" t="s">
+        <v>612</v>
+      </c>
+      <c r="J178" t="s">
+        <v>597</v>
+      </c>
+      <c r="K178" t="s">
         <v>610</v>
       </c>
-      <c r="J178" t="s">
-        <v>596</v>
-      </c>
-      <c r="K178" t="s">
-        <v>609</v>
-      </c>
       <c r="L178" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B178 B7829:B65536">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0" scaleWithDoc="0"/>
 </worksheet>
